--- a/results/05_transient_transcription_output/601/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/601/Midpoint_Excel_with_OCR_Results.xlsx
@@ -627,7 +627,7 @@
       <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -645,7 +645,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -669,14 +669,13 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="M4" s="2" t="n"/>
@@ -692,10 +691,14 @@
 </t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">2150
 </t>
         </is>
       </c>
@@ -707,7 +710,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -719,27 +722,18 @@
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="n"/>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>16</t>
         </is>
       </c>
       <c r="X4" s="2" t="n"/>
-      <c r="Y4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="Y4" s="2" t="n"/>
       <c r="Z4" s="2" t="n"/>
       <c r="AA4" t="inlineStr">
         <is>
@@ -769,61 +763,61 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10920
+          <t xml:space="preserve">928
 </t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -841,13 +835,13 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">619
+          <t xml:space="preserve">615
 </t>
         </is>
       </c>
@@ -857,15 +851,30 @@
 </t>
         </is>
       </c>
-      <c r="V5" s="2" t="n"/>
-      <c r="W5" s="2" t="n"/>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">184
 </t>
         </is>
       </c>
-      <c r="Y5" s="2" t="n"/>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">60
@@ -886,13 +895,13 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5089
+          <t xml:space="preserve">5082
 </t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">22441
 </t>
         </is>
       </c>
@@ -904,7 +913,8 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -915,7 +925,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -927,48 +937,43 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>418</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">1318
 </t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0920
-</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1928
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="n"/>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11458
+          <t xml:space="preserve">1436
 </t>
         </is>
       </c>
@@ -980,7 +985,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -992,7 +997,7 @@
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -1004,7 +1009,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -1016,7 +1021,7 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
@@ -1040,7 +1045,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5129
+          <t xml:space="preserve">529
 </t>
         </is>
       </c>
@@ -1052,18 +1057,19 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -1075,67 +1081,68 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1136
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">9837
 </t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">7181
 </t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1125
+          <t xml:space="preserve">425
 </t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">1776
 </t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>841</t>
+          <t xml:space="preserve">174
+</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1146,7 +1153,7 @@
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
@@ -1158,19 +1165,19 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">825
 </t>
         </is>
       </c>
@@ -1194,7 +1201,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2298
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -1212,72 +1219,67 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>56</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1959
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">950
+</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="n"/>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11205
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -1289,49 +1291,49 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">760
+</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">58
+</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">160
 </t>
         </is>
       </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1168
-</t>
-        </is>
-      </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">900
 </t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -1349,75 +1351,81 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t xml:space="preserve">249
+</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>185</t>
+          <t xml:space="preserve">11835
+</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6156
+          <t xml:space="preserve">676
 </t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="n"/>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>091</t>
+        </is>
+      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t xml:space="preserve">631
+</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2644</t>
+          <t xml:space="preserve">164
+</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">511
+          <t xml:space="preserve">17179190
+1
 </t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
+          <t xml:space="preserve">659
 </t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">459
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">1738
 </t>
         </is>
       </c>
@@ -1428,46 +1436,46 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>661</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>76</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>53010</t>
+          <t xml:space="preserve">30
+</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>401</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">451
 </t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
@@ -1502,35 +1510,40 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33
+</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">102
 </t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">147
@@ -1545,14 +1558,13 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>8801</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1563,56 +1575,61 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1940
-</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr"/>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">897
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10884
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -1630,12 +1647,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1548</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -1653,12 +1670,13 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>331</t>
+          <t xml:space="preserve">88
+</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1669,37 +1687,38 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">087
 </t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">14686
 </t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t xml:space="preserve">20
+</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1710,62 +1729,60 @@
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">22
+198
 </t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">399
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
+          <t>940</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1782,19 +1799,19 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2295
+          <t xml:space="preserve">2989
 </t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -1806,73 +1823,73 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1091
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">10
 </t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">945
 </t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1171
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -1884,42 +1901,44 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">745
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1638
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t xml:space="preserve">850
+</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>401</t>
+          <t xml:space="preserve">28
+</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1936,13 +1955,13 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293220
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">636
 </t>
         </is>
       </c>
@@ -1960,7 +1979,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">498
 </t>
         </is>
       </c>
@@ -1972,17 +1991,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr"/>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="n"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">150
@@ -1997,78 +2016,74 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>9464</t>
-        </is>
-      </c>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="n"/>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1582
+</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1685
+</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">158
 </t>
         </is>
       </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">018
-</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
+          <t xml:space="preserve">928
 </t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -2084,12 +2099,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3240
-</t>
-        </is>
-      </c>
+      <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">218
@@ -2098,7 +2108,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -2110,19 +2120,19 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -2132,7 +2142,12 @@
 </t>
         </is>
       </c>
-      <c r="K14" s="2" t="n"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">53
+</t>
+        </is>
+      </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">144
@@ -2147,20 +2162,25 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1583
-</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="n"/>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
+          <t xml:space="preserve">1413
 </t>
         </is>
       </c>
@@ -2172,49 +2192,49 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1719
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1712
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -2232,37 +2252,41 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3079
+          <t xml:space="preserve">14755
 </t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="n"/>
+          <t>451</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">1121
 </t>
         </is>
       </c>
@@ -2274,37 +2298,26 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">968
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="n"/>
+      <c r="O15" s="2" t="n"/>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2321,13 +2334,13 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
+          <t xml:space="preserve">3730
 </t>
         </is>
       </c>
@@ -2339,31 +2352,31 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8855
+          <t xml:space="preserve">3410
 </t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -2381,19 +2394,19 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14259
+          <t xml:space="preserve">1416
 </t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>684</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2403,13 +2416,13 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11074
+          <t xml:space="preserve">474
 </t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>6441</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2419,84 +2432,93 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">732
 </t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">694
+</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="n"/>
+          <t xml:space="preserve">5117
+18
+</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">60
+</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>234</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t xml:space="preserve">880
+</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>324</t>
+          <t xml:space="preserve">39945
+</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>448</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">843
 </t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>561</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">482
 </t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -2514,25 +2536,25 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">1343
 </t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">1481
 </t>
         </is>
       </c>
@@ -2544,55 +2566,54 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">79
+</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">139
+</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">12
 </t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">746
-</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
@@ -2610,40 +2631,43 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">789
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1845
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>286</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>502</t>
+          <t xml:space="preserve">91
+</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -2661,19 +2685,18 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2250
+          <t xml:space="preserve">4285
 </t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -2685,19 +2708,30 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>184</t>
+          <t xml:space="preserve">14
+</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>00</t>
+          <t xml:space="preserve">187
+</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2708,35 +2742,38 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t xml:space="preserve">920
+</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr"/>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t xml:space="preserve">218
+</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t xml:space="preserve">178
+</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>181</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
@@ -2752,32 +2789,28 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
-</t>
+          <t>810</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2794,7 +2827,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4285
+          <t xml:space="preserve">4406
 </t>
         </is>
       </c>
@@ -2812,19 +2845,19 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">1952
 </t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -2836,13 +2869,13 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -2854,25 +2887,15 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1542
-</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="n"/>
+      <c r="O19" s="2" t="n"/>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">514
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -2890,47 +2913,50 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">540
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>181</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t xml:space="preserve">8105
+</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>401</t>
+          <t xml:space="preserve">44
+</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2947,31 +2973,31 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4406
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">769
 </t>
         </is>
       </c>
@@ -2982,15 +3008,10 @@
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
+      <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
@@ -3002,79 +3023,81 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">112
+7
 </t>
         </is>
       </c>
       <c r="O20" s="2" t="n"/>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>125</t>
+          <t xml:space="preserve">185
+</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">768
+          <t xml:space="preserve">468
 </t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1672
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -3092,25 +3115,25 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531
+          <t xml:space="preserve">24617
 </t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">2419
 </t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -3122,11 +3145,16 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr"/>
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">115
@@ -3135,7 +3163,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -3153,20 +3181,25 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970
-</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="n"/>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">2414
 </t>
         </is>
       </c>
@@ -3184,43 +3217,43 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">748
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -3238,19 +3271,19 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2617
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">2066
 </t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -3262,115 +3295,105 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="n"/>
+      <c r="O22" s="2" t="n"/>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70
+</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">85
-</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1125
-</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">918
-</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="n"/>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1178
-</t>
-        </is>
-      </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">562
 </t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="X22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="n"/>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">945
+          <t xml:space="preserve">455
 </t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -3388,7 +3411,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233
+          <t xml:space="preserve">1477
 </t>
         </is>
       </c>
@@ -3398,11 +3421,14 @@
 </t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr"/>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3411,23 +3437,15 @@
 </t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>6170</t>
-        </is>
-      </c>
+      <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>33211</t>
-        </is>
-      </c>
+          <t xml:space="preserve">73
+</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">762
@@ -3437,25 +3455,25 @@
       <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1090
+          <t xml:space="preserve">1798
 </t>
         </is>
       </c>
@@ -3473,7 +3491,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4141</t>
+          <t>419</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3484,31 +3502,29 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>442</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t xml:space="preserve">23
+</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4995
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>1581</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3525,8 +3541,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14779
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3537,7 +3552,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -3549,15 +3564,11 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr">
         <is>
           <t>15</t>
@@ -3569,15 +3580,10 @@
 </t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+      <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -3587,27 +3593,18 @@
 </t>
         </is>
       </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
+      <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
-</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">16
+111
+</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr"/>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3619,13 +3616,13 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">1281
 </t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -3637,30 +3634,32 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t xml:space="preserve">183
+</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">1111
 </t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">871
+          <t xml:space="preserve">940
 </t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>1581</t>
+          <t xml:space="preserve">28
+</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3677,84 +3676,80 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>97</t>
+          <t xml:space="preserve">226
+</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>961</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>146</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>901</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="n"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
+          <t>451</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">915
-</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr"/>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="n"/>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>11454</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr"/>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>116</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
@@ -3770,31 +3765,31 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -3812,13 +3807,13 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8904
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1225
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -3830,19 +3825,19 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1891
 </t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>138</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3859,13 +3854,14 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">81
+1198
 </t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1846
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
@@ -3877,19 +3873,19 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">406
 </t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -3901,7 +3897,7 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1175
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
@@ -3913,7 +3909,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17130
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -3925,7 +3921,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -3936,19 +3932,19 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -3966,13 +3962,13 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3260
+          <t xml:space="preserve">535
 </t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -3990,7 +3986,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -4009,44 +4005,49 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr"/>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1950
+          <t xml:space="preserve">950
 </t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2108
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -4058,19 +4059,19 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">780
+          <t xml:space="preserve">70
 </t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -4082,19 +4083,19 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">838
 </t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -4112,31 +4113,31 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2818
+          <t xml:space="preserve">2898
 </t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1538
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -4148,19 +4149,20 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">9799791979277
+2 8
 </t>
         </is>
       </c>
@@ -4172,13 +4174,13 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -4190,13 +4192,13 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">2108
 </t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -4208,13 +4210,13 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1768
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">728
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -4226,7 +4228,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -4238,19 +4240,19 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">1851
 </t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8308
+          <t xml:space="preserve">850
 </t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -4268,13 +4270,13 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23059
+          <t xml:space="preserve">1999
 </t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11219
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -4286,7 +4288,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -4304,80 +4306,75 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1849
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
+          <t>7144</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr"/>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1121
+</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="O29" s="2" t="n"/>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1821
-</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -4387,16 +4384,10 @@
 </t>
         </is>
       </c>
-      <c r="X29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
+      <c r="X29" s="2" t="n"/>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>1474</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -4419,7 +4410,8 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2898
+          <t xml:space="preserve">1921
+188181
 </t>
         </is>
       </c>
@@ -4428,62 +4420,67 @@
           <t>7162</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">686
+</t>
+        </is>
+      </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
+          <t xml:space="preserve">9661
 </t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>45700</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">666
-</t>
+          <t>66611</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115656
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>3501</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7197
+</t>
+        </is>
+      </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">717
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>201</t>
+          <t xml:space="preserve">10
+</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10562
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
@@ -4492,30 +4489,53 @@
           <t>8244</t>
         </is>
       </c>
-      <c r="S30" s="2" t="n"/>
-      <c r="T30" s="2" t="n"/>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">368883
+101
+</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9242175
+993 6
+</t>
+        </is>
+      </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2461</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="W30" s="2" t="n"/>
-      <c r="X30" s="2" t="n"/>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>841</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">777
+1
+17
+</t>
+        </is>
+      </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>144</t>
+          <t xml:space="preserve">83
+</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>751</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4532,13 +4552,13 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4578,11 +4598,15 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -4591,27 +4615,16 @@
 </t>
         </is>
       </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11705
-</t>
-        </is>
-      </c>
+      <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">941
-</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr"/>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -4623,16 +4636,11 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">723
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">7900
+</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="n"/>
       <c r="U31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">69
@@ -4641,31 +4649,28 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="X31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr"/>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">883
+          <t xml:space="preserve">221
+710
 </t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4682,13 +4687,13 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3220
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
@@ -4700,64 +4705,66 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>131</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">11
+</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="n"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>4451</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78
+</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>310</t>
+          <t xml:space="preserve">30
+</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -4769,20 +4776,19 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">515
 </t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -4799,14 +4805,19 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="Y32" s="2" t="inlineStr"/>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">808
+</t>
+        </is>
+      </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -4824,13 +4835,13 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2355
+          <t xml:space="preserve">4828
 </t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -4842,25 +4853,25 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1882
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8786
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -4872,13 +4883,13 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1157
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
@@ -4890,55 +4901,56 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">177
+1
+</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7144
+</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">930
-</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1248
-</t>
-        </is>
-      </c>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
-      <c r="T33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">515
-</t>
-        </is>
-      </c>
-      <c r="U33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11144
-</t>
-        </is>
-      </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -4950,19 +4962,20 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
+          <t xml:space="preserve">14
+247
 </t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -4986,13 +4999,14 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">4241
 </t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>06</t>
+          <t xml:space="preserve">115
+</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -5003,13 +5017,14 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">112179 1
+</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -5024,12 +5039,7 @@
 </t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
+      <c r="K34" s="2" t="n"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">125
@@ -5038,43 +5048,44 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4116
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">14181
+60
 </t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -5086,13 +5097,13 @@
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -5104,16 +5115,11 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1167
-</t>
-        </is>
-      </c>
-      <c r="Y34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1851
+</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="n"/>
       <c r="Z34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">42
@@ -5134,36 +5140,36 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4828
+          <t xml:space="preserve">4928
 </t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112150
+          <t xml:space="preserve">1501
 </t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>436</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">1937
 </t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1894
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -5181,7 +5187,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -5193,31 +5199,26 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1155
-</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="n"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">9180
 </t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">845
+          <t xml:space="preserve">1457
 </t>
         </is>
       </c>
@@ -5229,43 +5230,43 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6009
+          <t xml:space="preserve">608
 </t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1207
+          <t xml:space="preserve">12067
 </t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">1661
 </t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">758
+          <t xml:space="preserve">798
 </t>
         </is>
       </c>
@@ -5289,31 +5290,31 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4928
+          <t xml:space="preserve">4989
 </t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1539
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1981
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -5325,13 +5326,13 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">2235
 </t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -5349,31 +5350,16 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">115
-</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="n"/>
+      <c r="O36" s="2" t="n"/>
+      <c r="P36" s="2" t="n"/>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2141
+          <t xml:space="preserve">1441
 </t>
         </is>
       </c>
@@ -5385,22 +5371,17 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">551
-</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">581
+</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="n"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">184
@@ -5413,21 +5394,15 @@
 </t>
         </is>
       </c>
-      <c r="X36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
+      <c r="X36" s="2" t="n"/>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -5445,25 +5420,22 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4989
-</t>
+          <t>9280</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>1194</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">658
-</t>
+          <t>768</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
-</t>
+          <t>926</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -5474,47 +5446,38 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">619
+          <t xml:space="preserve">6139
 </t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11106
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1757
-</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">702
-</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
+          <t xml:space="preserve">757
+</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="n"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1490
+          <t xml:space="preserve">44980
 </t>
         </is>
       </c>
@@ -5526,54 +5489,53 @@
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">871
 </t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t xml:space="preserve">314
+</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2348
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8098
+          <t xml:space="preserve">8048
 </t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
-</t>
-        </is>
-      </c>
-      <c r="Y37" s="2" t="inlineStr"/>
+          <t>852</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="n"/>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -5591,7 +5553,8 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>24923</t>
+          <t xml:space="preserve">4
+</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -5608,25 +5571,25 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -5636,51 +5599,40 @@
 </t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="n"/>
+      <c r="M38" s="2" t="n"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">899
+</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61718682
+68
+8987
+</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4 8
+21 0
+</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">151
-</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">227
-</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
+14
 </t>
         </is>
       </c>
@@ -5692,16 +5644,11 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">647
+</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="n"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">182
@@ -5716,7 +5663,7 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1731
+          <t xml:space="preserve">1721
 </t>
         </is>
       </c>
@@ -5746,19 +5693,19 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4386
+          <t xml:space="preserve">583
 </t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -5769,7 +5716,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>71</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -5778,41 +5725,23 @@
 </t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32
-</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
+      <c r="I39" s="2" t="n"/>
+      <c r="J39" s="2" t="n"/>
+      <c r="K39" s="2" t="n"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>501</t>
+          <t xml:space="preserve">141
+</t>
         </is>
       </c>
       <c r="N39" s="2" t="n"/>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">898
-</t>
-        </is>
-      </c>
+      <c r="O39" s="2" t="n"/>
       <c r="P39" s="2" t="inlineStr">
         <is>
           <t>18</t>
@@ -5820,45 +5749,37 @@
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">1536
 </t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>77</t>
+          <t xml:space="preserve">116
+</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="T39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">520
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">22
+1501
+</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="n"/>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11911
-</t>
-        </is>
-      </c>
-      <c r="W39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="n"/>
       <c r="X39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">158
@@ -5867,13 +5788,13 @@
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">714
 </t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>641</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5890,12 +5811,13 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>54521</t>
+          <t xml:space="preserve">5451
+</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
@@ -5919,76 +5841,69 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>715</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1481
-</t>
+          <t>466</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1136
-</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
+          <t>50</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="n"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+8917
+</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">11
 </t>
         </is>
       </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">585
@@ -5997,7 +5912,7 @@
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -6015,13 +5930,13 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">720
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -6061,33 +5976,23 @@
 </t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1112
-</t>
-        </is>
-      </c>
+      <c r="F41" s="2" t="n"/>
+      <c r="G41" s="2" t="n"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">23530
 </t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
@@ -6099,20 +6004,26 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">1481
 </t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1389
-</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="n"/>
+          <t xml:space="preserve">13536
+</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">889
+</t>
+        </is>
+      </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 111
+          <t xml:space="preserve">1
+6
 </t>
         </is>
       </c>
@@ -6124,19 +6035,19 @@
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">2382
 </t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -6154,13 +6065,13 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1960
 </t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
@@ -6202,13 +6113,14 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">191
+181
 </t>
         </is>
       </c>
@@ -6226,50 +6138,56 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6146
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16211
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
-</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="n"/>
+          <t xml:space="preserve">137
+</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2924
+991
+</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">87701
 </t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -6281,7 +6199,7 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1671
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -6293,37 +6211,37 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">605
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">16585
 </t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
@@ -6347,145 +6265,145 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">53109
+          <t xml:space="preserve">570
 </t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2392
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1131
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">18070
+</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1211
+</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01
+</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">151
+</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3170
+</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1128
+</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">115
+</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">588
+</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">181
 </t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1114
-</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42
-</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1184
-</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1910
-</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1222
-</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">580
-</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7240
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">537
 </t>
         </is>
       </c>
@@ -6503,139 +6421,144 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8571
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">634
 </t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42
+</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2008
+</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5409
+</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9271
+</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">595
+</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">108
 </t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1114
-</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50
-</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1836
-</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1896
-</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5408
-</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">918
-</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1595
-</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1108
-</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1118
+</t>
+        </is>
+      </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">958
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>1668</t>
+          <t xml:space="preserve">780
+</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
@@ -6653,29 +6576,31 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2283
+          <t xml:space="preserve">2830
 </t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">133
+</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>105</t>
+          <t xml:space="preserve">124
+</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6210
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
@@ -6687,55 +6612,49 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">2152
 </t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8985
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8511
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5409
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr"/>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
@@ -6746,19 +6665,19 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9756
+          <t xml:space="preserve">9792
 </t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35611
+          <t xml:space="preserve">3511
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">690
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -6770,23 +6689,27 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">92926
 </t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
-        </is>
-      </c>
-      <c r="Z45" s="2" t="n"/>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">287
+</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -6807,25 +6730,21 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">133
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">818
+4236
+</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="n"/>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -6847,23 +6766,23 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="2" t="n"/>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="2" t="n"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -6881,7 +6800,7 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1718
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -6893,13 +6812,13 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">585
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -6910,10 +6829,16 @@
 </t>
         </is>
       </c>
-      <c r="X46" s="2" t="inlineStr"/>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>69</t>
+          <t xml:space="preserve">78
+</t>
         </is>
       </c>
       <c r="Z46" s="2" t="n"/>
@@ -6929,39 +6854,56 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
       <c r="G47" t="inlineStr">
         <is>
           <t xml:space="preserve">1
 </t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">138
 </t>
         </is>
       </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t xml:space="preserve">11984
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">4
+27
+78
+1
+646 7
 </t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t xml:space="preserve">114146
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
+1
+1
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/601/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/601/Midpoint_Excel_with_OCR_Results.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5823
+          <t xml:space="preserve">5829
 </t>
         </is>
       </c>
@@ -642,7 +642,12 @@
 </t>
         </is>
       </c>
-      <c r="F4" s="2" t="n"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">115
@@ -651,25 +656,54 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="n"/>
-      <c r="J4" s="2" t="n"/>
-      <c r="K4" s="2" t="n"/>
+          <t xml:space="preserve">131
+</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>451</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="n"/>
-      <c r="N4" s="2" t="n"/>
-      <c r="O4" s="2" t="n"/>
+          <t xml:space="preserve">117
+</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">131
+</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">870
+</t>
+        </is>
+      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">22
+</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -690,12 +724,26 @@
 </t>
         </is>
       </c>
-      <c r="T4" s="2" t="n"/>
-      <c r="U4" s="2" t="n"/>
-      <c r="V4" s="2" t="n"/>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1520
+</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11207
+</t>
+        </is>
+      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -716,27 +764,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3888
-</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n"/>
+          <t xml:space="preserve">2889
+</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1108
+</t>
+        </is>
+      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">872
-</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="n"/>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">1123
 </t>
         </is>
       </c>
@@ -748,24 +806,59 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="n"/>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="n"/>
-      <c r="N5" s="2" t="n"/>
-      <c r="O5" s="2" t="n"/>
-      <c r="P5" s="2" t="n"/>
-      <c r="Q5" s="2" t="n"/>
-      <c r="R5" s="2" t="n"/>
-      <c r="S5" s="2" t="n"/>
+          <t xml:space="preserve">135
+</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">224
+</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr"/>
       <c r="T5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">520
@@ -786,7 +879,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -796,7 +889,12 @@
 </t>
         </is>
       </c>
-      <c r="Y5" s="2" t="n"/>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">755
+</t>
+        </is>
+      </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">60
@@ -817,45 +915,106 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25089
-</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
+          <t xml:space="preserve">5089
+</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>136</t>
+          <t xml:space="preserve">1180
+</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="n"/>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
-</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="n"/>
-      <c r="L6" s="2" t="n"/>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1138
+</t>
+        </is>
+      </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">130
 </t>
         </is>
       </c>
-      <c r="N6" s="2" t="n"/>
-      <c r="O6" s="2" t="n"/>
-      <c r="P6" s="2" t="n"/>
-      <c r="Q6" s="2" t="n"/>
-      <c r="R6" s="2" t="n"/>
-      <c r="S6" s="2" t="n"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">619
@@ -870,23 +1029,28 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="Y6" s="2" t="n"/>
+          <t xml:space="preserve">1181
+</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">870
+</t>
+        </is>
+      </c>
       <c r="Z6" s="2" t="n"/>
       <c r="AA6" t="inlineStr">
         <is>
@@ -906,7 +1070,12 @@
 </t>
         </is>
       </c>
-      <c r="D7" s="2" t="n"/>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">132
@@ -915,48 +1084,80 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">11898
+</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107
+</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1236
+</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">188
 </t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="n"/>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="n"/>
-      <c r="L7" s="2" t="n"/>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="n"/>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>410</t>
+          <t xml:space="preserve">5930
+</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="n"/>
-      <c r="R7" s="2" t="n"/>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -968,20 +1169,40 @@
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11918
-</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="n"/>
+          <t xml:space="preserve">1118
+</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="X7" s="2" t="n"/>
-      <c r="Y7" s="2" t="n"/>
-      <c r="Z7" s="2" t="n"/>
+          <t xml:space="preserve">1166
+</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">821
+</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01
+</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>4</t>
@@ -1000,10 +1221,15 @@
 </t>
         </is>
       </c>
-      <c r="D8" s="2" t="n"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">419
+</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
@@ -1019,7 +1245,12 @@
 </t>
         </is>
       </c>
-      <c r="H8" s="2" t="n"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">18
@@ -1034,7 +1265,8 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>77</t>
+          <t xml:space="preserve">272
+</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1049,31 +1281,66 @@
 </t>
         </is>
       </c>
-      <c r="N8" s="2" t="n"/>
-      <c r="O8" s="2" t="n"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">08
 </t>
         </is>
       </c>
-      <c r="Q8" s="2" t="n"/>
-      <c r="R8" s="2" t="n"/>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">205
+</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="n"/>
+          <t xml:space="preserve">1181
+</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">760
+</t>
+        </is>
+      </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="n"/>
-      <c r="W8" s="2" t="n"/>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
       <c r="X8" s="2" t="n"/>
       <c r="Y8" s="2" t="n"/>
       <c r="Z8" s="2" t="n"/>
@@ -1103,7 +1370,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">676
+          <t xml:space="preserve">616
 </t>
         </is>
       </c>
@@ -1115,35 +1382,58 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2694</t>
+          <t xml:space="preserve">8815
+</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>634</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr"/>
+          <t xml:space="preserve">651
+</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">511
-</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="n"/>
+          <t xml:space="preserve">311
+</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">607
+</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="n"/>
+          <t xml:space="preserve">860
+</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9590
+</t>
+        </is>
+      </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">66
@@ -1152,24 +1442,47 @@
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11140
-</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="n"/>
-      <c r="S9" s="2" t="n"/>
-      <c r="T9" s="2" t="n"/>
-      <c r="U9" s="2" t="n"/>
+          <t xml:space="preserve">11940
+</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">881
+</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1862
+</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>5776</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1530
+</t>
+        </is>
+      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="n"/>
+          <t xml:space="preserve">15940
+</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>7581</t>
+        </is>
+      </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
@@ -1179,7 +1492,12 @@
 </t>
         </is>
       </c>
-      <c r="Z9" s="2" t="n"/>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1193,46 +1511,107 @@
         </is>
       </c>
       <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" s="2" t="n"/>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="n"/>
-      <c r="J10" s="2" t="n"/>
-      <c r="K10" s="2" t="n"/>
-      <c r="L10" s="2" t="n"/>
-      <c r="M10" s="2" t="n"/>
-      <c r="N10" s="2" t="n"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">511
+</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1916
+</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1209
+</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4590
-</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="n"/>
-      <c r="Q10" s="2" t="n"/>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1081
+</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">858
+</t>
+        </is>
+      </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="n"/>
-      <c r="T10" s="2" t="n"/>
+          <t xml:space="preserve">801
+</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">068
+</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21626
+</t>
+        </is>
+      </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t xml:space="preserve">220
+</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">9590
 </t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8908
+          <t xml:space="preserve">0098
 </t>
         </is>
       </c>
@@ -1244,13 +1623,13 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4150
+          <t xml:space="preserve">4198
 </t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>
@@ -1268,7 +1647,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94450
+          <t xml:space="preserve">4490
 </t>
         </is>
       </c>
@@ -1302,14 +1681,19 @@
 </t>
         </is>
       </c>
-      <c r="I11" s="2" t="n"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">33
 </t>
         </is>
       </c>
-      <c r="K11" s="2" t="n"/>
+      <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">147
@@ -1324,18 +1708,28 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="n"/>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">918
+</t>
+        </is>
+      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="n"/>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12218
+</t>
+        </is>
+      </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">176
@@ -1348,7 +1742,12 @@
 </t>
         </is>
       </c>
-      <c r="T11" s="2" t="n"/>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">629
+</t>
+        </is>
+      </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">106
@@ -1357,7 +1756,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -1394,18 +1793,28 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2918
-</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n"/>
+          <t xml:space="preserve">2218
+</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225
+</t>
+        </is>
+      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="n"/>
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">88
@@ -1418,67 +1827,113 @@
 </t>
         </is>
       </c>
-      <c r="I12" s="2" t="n"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="n"/>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1108
+</t>
+        </is>
+      </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="n"/>
-      <c r="O12" s="2" t="n"/>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">2104
+</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1884
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="n"/>
-      <c r="W12" s="2" t="n"/>
-      <c r="X12" s="2" t="n"/>
-      <c r="Y12" s="2" t="n"/>
-      <c r="Z12" s="2" t="n"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1157
+</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">940
+</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>7</t>
@@ -1491,13 +1946,33 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="n"/>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2290
+</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">224
+</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -1519,24 +1994,54 @@
 </t>
         </is>
       </c>
-      <c r="K13" s="2" t="n"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="n"/>
-      <c r="N13" s="2" t="n"/>
-      <c r="O13" s="2" t="n"/>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1835
+</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">928
+</t>
+        </is>
+      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="n"/>
-      <c r="R13" s="2" t="n"/>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">205
+</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">177
@@ -1545,7 +2050,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">745
 </t>
         </is>
       </c>
@@ -1557,25 +2062,25 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
+          <t xml:space="preserve">2408
 </t>
         </is>
       </c>
@@ -1592,62 +2097,140 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="n"/>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3220
+</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">236
+</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1188
+</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">151
+</t>
+        </is>
+      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="n"/>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">150
 </t>
         </is>
       </c>
-      <c r="M14" s="2" t="n"/>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="n"/>
-      <c r="P14" s="2" t="n"/>
-      <c r="Q14" s="2" t="n"/>
-      <c r="R14" s="2" t="n"/>
-      <c r="S14" s="2" t="n"/>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">945
+</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1158
+</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">905
 </t>
         </is>
       </c>
       <c r="U14" s="2" t="n"/>
-      <c r="V14" s="2" t="n"/>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
-        </is>
-      </c>
-      <c r="X14" s="2" t="n"/>
-      <c r="Y14" s="2" t="n"/>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">151
+</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800
+</t>
+        </is>
+      </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -1663,26 +2246,61 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3240
+</t>
+        </is>
+      </c>
       <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="n"/>
-      <c r="F15" s="2" t="n"/>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">84
 </t>
         </is>
       </c>
-      <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="n"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1214
+</t>
+        </is>
+      </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">117
 </t>
         </is>
       </c>
-      <c r="K15" s="2" t="n"/>
-      <c r="L15" s="2" t="n"/>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">137
@@ -1691,37 +2309,82 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="n"/>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">940
+</t>
+        </is>
+      </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="n"/>
-      <c r="R15" s="2" t="n"/>
-      <c r="S15" s="2" t="n"/>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">719
 </t>
         </is>
       </c>
-      <c r="U15" s="2" t="n"/>
-      <c r="V15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72
+</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="X15" s="2" t="n"/>
-      <c r="Y15" s="2" t="n"/>
-      <c r="Z15" s="2" t="n"/>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>10</t>
@@ -1734,55 +2397,113 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n"/>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3079
+</t>
+        </is>
+      </c>
       <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="n"/>
-      <c r="F16" s="2" t="n"/>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>783</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="n"/>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="n"/>
-      <c r="M16" s="2" t="n"/>
+          <t xml:space="preserve">59
+</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>1481</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">969
+          <t xml:space="preserve">968
 </t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="n"/>
-      <c r="R16" s="2" t="n"/>
-      <c r="S16" s="2" t="n"/>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">730
 </t>
         </is>
       </c>
-      <c r="U16" s="2" t="n"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">166
@@ -1795,10 +2516,15 @@
 </t>
         </is>
       </c>
-      <c r="X16" s="2" t="n"/>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">875
 </t>
         </is>
       </c>
@@ -1823,31 +2549,31 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11148
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1674
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">911
 </t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1474
+          <t xml:space="preserve">474
 </t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">6494
+</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1858,7 +2584,8 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t xml:space="preserve">69
+</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1869,81 +2596,90 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>196</t>
+          <t xml:space="preserve">1912
+</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1694
+          <t xml:space="preserve">694
 </t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1164646</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="n"/>
+          <t>11642</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">648
+</t>
+        </is>
+      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t xml:space="preserve">60
+</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0962
+          <t xml:space="preserve">969
 </t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0828
+          <t xml:space="preserve">838
 </t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8880
+          <t xml:space="preserve">884
 </t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3245</t>
+          <t xml:space="preserve">1648
+</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t xml:space="preserve">845
+</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17186
+          <t xml:space="preserve">1806
 </t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">861
+          <t xml:space="preserve">851
 </t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24208
+          <t xml:space="preserve">4888
 </t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -1967,16 +2703,30 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
-</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="n"/>
-      <c r="F18" s="2" t="n"/>
-      <c r="G18" s="2" t="n"/>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1418
+</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">95
+</t>
+        </is>
+      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -1988,14 +2738,15 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="n"/>
+          <t xml:space="preserve">4214
+</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>346</t>
+          <t xml:space="preserve">146
+</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2004,33 +2755,54 @@
 </t>
         </is>
       </c>
-      <c r="N18" s="2" t="n"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="n"/>
-      <c r="Q18" s="2" t="n"/>
+          <t xml:space="preserve">929
+</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4161</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">789
-</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="n"/>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">169
@@ -2043,8 +2815,18 @@
 </t>
         </is>
       </c>
-      <c r="X18" s="2" t="n"/>
-      <c r="Y18" s="2" t="n"/>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">901
+</t>
+        </is>
+      </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">20
@@ -2065,22 +2847,28 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4285
+          <t xml:space="preserve">4288
 </t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="n"/>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">124
@@ -2089,18 +2877,43 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
-</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="n"/>
-      <c r="J19" s="2" t="n"/>
-      <c r="K19" s="2" t="n"/>
-      <c r="L19" s="2" t="n"/>
-      <c r="M19" s="2" t="n"/>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -2118,14 +2931,25 @@
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="n"/>
-      <c r="S19" s="2" t="n"/>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1691
+          <t xml:space="preserve">691
 </t>
         </is>
       </c>
@@ -2135,18 +2959,28 @@
 </t>
         </is>
       </c>
-      <c r="V19" s="2" t="n"/>
-      <c r="W19" s="2" t="n"/>
-      <c r="X19" s="2" t="n"/>
+      <c r="V19" s="2" t="inlineStr"/>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1150
+</t>
+        </is>
+      </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
@@ -2164,21 +2998,30 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24406
+          <t xml:space="preserve">8406
 </t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="n"/>
-      <c r="F20" s="2" t="n"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -2188,12 +3031,42 @@
 </t>
         </is>
       </c>
-      <c r="I20" s="2" t="n"/>
-      <c r="J20" s="2" t="n"/>
-      <c r="K20" s="2" t="n"/>
-      <c r="L20" s="2" t="n"/>
-      <c r="M20" s="2" t="n"/>
-      <c r="N20" s="2" t="n"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">151
+</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">115
+</t>
+        </is>
+      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">920
@@ -2202,35 +3075,65 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="n"/>
-      <c r="R20" s="2" t="n"/>
-      <c r="S20" s="2" t="n"/>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">599
+          <t xml:space="preserve">540
 </t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
-</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="n"/>
-      <c r="W20" s="2" t="n"/>
-      <c r="X20" s="2" t="n"/>
+          <t xml:space="preserve">1144
+</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1198
+</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr"/>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1188
+</t>
+        </is>
+      </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
-        </is>
-      </c>
-      <c r="Z20" s="2" t="n"/>
+          <t xml:space="preserve">810
+</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">274
+</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>13</t>
@@ -2255,58 +3158,133 @@
 </t>
         </is>
       </c>
-      <c r="E21" s="2" t="n"/>
-      <c r="F21" s="2" t="n"/>
-      <c r="G21" s="2" t="n"/>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1149
+</t>
+        </is>
+      </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">238
 </t>
         </is>
       </c>
-      <c r="I21" s="2" t="n"/>
-      <c r="J21" s="2" t="n"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">56
 </t>
         </is>
       </c>
-      <c r="L21" s="2" t="n"/>
-      <c r="M21" s="2" t="n"/>
-      <c r="N21" s="2" t="n"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1194
+</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">151
+</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970
-</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="n"/>
-      <c r="Q21" s="2" t="n"/>
-      <c r="R21" s="2" t="n"/>
-      <c r="S21" s="2" t="n"/>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05
+</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">768
 </t>
         </is>
       </c>
-      <c r="U21" s="2" t="n"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
-</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="n"/>
-      <c r="X21" s="2" t="n"/>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920
-</t>
-        </is>
-      </c>
-      <c r="Z21" s="2" t="n"/>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>14</t>
@@ -2321,29 +3299,49 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12617
+          <t xml:space="preserve">2617
 </t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="n"/>
-      <c r="F22" s="2" t="n"/>
-      <c r="G22" s="2" t="n"/>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">147
+</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74
+</t>
+        </is>
+      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="n"/>
+          <t xml:space="preserve">1419
+</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2119
+</t>
+        </is>
+      </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -2353,23 +3351,48 @@
 </t>
         </is>
       </c>
-      <c r="L22" s="2" t="n"/>
-      <c r="M22" s="2" t="n"/>
-      <c r="N22" s="2" t="n"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">908
 </t>
         </is>
       </c>
-      <c r="P22" s="2" t="n"/>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="n"/>
+          <t xml:space="preserve">1215
+</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">189
@@ -2384,16 +3407,31 @@
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="n"/>
-      <c r="W22" s="2" t="n"/>
-      <c r="X22" s="2" t="n"/>
+          <t xml:space="preserve">6 8
+</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8709
+          <t xml:space="preserve">8809
 </t>
         </is>
       </c>
@@ -2423,64 +3461,94 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206
-</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="n"/>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1944
+</t>
+        </is>
+      </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">175
 </t>
         </is>
       </c>
-      <c r="G23" s="2" t="n"/>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">934
+          <t xml:space="preserve">4134
 </t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr"/>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05
+</t>
+        </is>
+      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="n"/>
-      <c r="M23" s="2" t="n"/>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1204
-</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="n"/>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1178
@@ -2499,18 +3567,33 @@
 </t>
         </is>
       </c>
-      <c r="V23" s="2" t="n"/>
-      <c r="W23" s="2" t="n"/>
-      <c r="X23" s="2" t="n"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">949
+          <t xml:space="preserve">945
 </t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -2528,77 +3611,84 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19832
+          <t xml:space="preserve">19212
 </t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1131
+          <t xml:space="preserve">111531
 </t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
+          <t xml:space="preserve">494
 </t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">9408
 </t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9437
+          <t xml:space="preserve">431
 </t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6444</t>
+          <t xml:space="preserve">698
+</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">808
 </t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3321</t>
+          <t xml:space="preserve">382
+</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171621
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t xml:space="preserve">1221
+</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">804618
-</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="n"/>
+          <t xml:space="preserve">8164
+</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -2628,33 +3718,38 @@
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>4064</t>
+          <t xml:space="preserve">406
+</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">9189
 </t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t xml:space="preserve">899
+</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t xml:space="preserve">9118
+</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>465</t>
+          <t xml:space="preserve">484
+</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t xml:space="preserve">1138
+</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -2671,7 +3766,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2354
+          <t xml:space="preserve">2154
 </t>
         </is>
       </c>
@@ -2683,26 +3778,27 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
-</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="n"/>
+          <t xml:space="preserve">139
+</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1183
+</t>
+        </is>
+      </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">87
 </t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
+      <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2711,32 +3807,46 @@
 </t>
         </is>
       </c>
-      <c r="K25" s="2" t="n"/>
-      <c r="L25" s="2" t="n"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">144
 </t>
         </is>
       </c>
-      <c r="N25" s="2" t="n"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="n"/>
+          <t xml:space="preserve">924
+</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>478</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -2745,17 +3855,42 @@
 </t>
         </is>
       </c>
-      <c r="T25" s="2" t="n"/>
-      <c r="U25" s="2" t="n"/>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">695
+</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81
+</t>
+        </is>
+      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">183
 </t>
         </is>
       </c>
-      <c r="W25" s="2" t="n"/>
-      <c r="X25" s="2" t="n"/>
-      <c r="Y25" s="2" t="n"/>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">871
+</t>
+        </is>
+      </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">28
@@ -2782,67 +3917,112 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="n"/>
+          <t xml:space="preserve">2126
+</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11211
+</t>
+        </is>
+      </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="n"/>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="n"/>
+          <t xml:space="preserve">2128
+</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="n"/>
+          <t xml:space="preserve">1181
+</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="n"/>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18492
+</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">9108
 </t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="n"/>
+          <t xml:space="preserve">2019
+</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
-</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr"/>
-      <c r="U26" s="2" t="n"/>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">689
+</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">166
@@ -2851,13 +4031,28 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="X26" s="2" t="n"/>
-      <c r="Y26" s="2" t="n"/>
-      <c r="Z26" s="2" t="n"/>
+          <t xml:space="preserve">1129
+</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">940
+</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>17</t>
@@ -2870,40 +4065,70 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n"/>
-      <c r="E27" s="2" t="n"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2260
+</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225
+</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="G27" s="2" t="n"/>
-      <c r="H27" s="2" t="n"/>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="n"/>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 5
+</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1846
 </t>
         </is>
       </c>
-      <c r="M27" s="2" t="n"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -2919,30 +4144,66 @@
 </t>
         </is>
       </c>
-      <c r="Q27" s="2" t="n"/>
-      <c r="R27" s="2" t="n"/>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">287
+</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">173
+</t>
+        </is>
+      </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">178
+</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1730
-</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="n"/>
+          <t xml:space="preserve">730
+</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="n"/>
-      <c r="X27" s="2" t="n"/>
-      <c r="Y27" s="2" t="n"/>
-      <c r="Z27" s="2" t="n"/>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1180
+</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">885
+</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>18</t>
@@ -2955,8 +4216,18 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2878
+</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">235
+</t>
+        </is>
+      </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">144
@@ -2969,17 +4240,27 @@
 </t>
         </is>
       </c>
-      <c r="G28" s="2" t="n"/>
-      <c r="H28" s="2" t="n"/>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91
+</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -2989,11 +4270,21 @@
 </t>
         </is>
       </c>
-      <c r="L28" s="2" t="n"/>
-      <c r="M28" s="2" t="n"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1154
+</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3005,30 +4296,70 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="n"/>
-      <c r="R28" s="2" t="n"/>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="n"/>
-      <c r="V28" s="2" t="n"/>
-      <c r="W28" s="2" t="n"/>
-      <c r="X28" s="2" t="n"/>
-      <c r="Y28" s="2" t="n"/>
-      <c r="Z28" s="2" t="n"/>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56
+</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>19</t>
@@ -3043,7 +4374,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3059
+          <t xml:space="preserve">20239
 </t>
         </is>
       </c>
@@ -3053,8 +4384,18 @@
 </t>
         </is>
       </c>
-      <c r="E29" s="2" t="n"/>
-      <c r="F29" s="2" t="n"/>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11179
+</t>
+        </is>
+      </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">80
@@ -3063,7 +4404,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -3073,43 +4414,106 @@
 </t>
         </is>
       </c>
-      <c r="J29" s="2" t="n"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="n"/>
-      <c r="M29" s="2" t="n"/>
+          <t xml:space="preserve">1654
+</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">147
+</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1950
-</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="n"/>
-      <c r="Q29" s="2" t="n"/>
-      <c r="R29" s="2" t="n"/>
-      <c r="S29" s="2" t="n"/>
+          <t xml:space="preserve">950
+</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">205
+</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="n"/>
-      <c r="V29" s="2" t="n"/>
-      <c r="W29" s="2" t="n"/>
-      <c r="X29" s="2" t="n"/>
-      <c r="Y29" s="2" t="n"/>
-      <c r="Z29" s="2" t="n"/>
+          <t xml:space="preserve">728
+</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">838
+</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>20</t>
@@ -3130,77 +4534,137 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1219
-</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="n"/>
-      <c r="F30" s="2" t="n"/>
-      <c r="G30" s="2" t="n"/>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">950
+</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">700
+</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78
+</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">188
 </t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="n"/>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1148
-</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="n"/>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">950
-</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="n"/>
-      <c r="Q30" s="2" t="n"/>
-      <c r="R30" s="2" t="n"/>
-      <c r="S30" s="2" t="n"/>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="n"/>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="W30" s="2" t="n"/>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1822009
-</t>
-        </is>
-      </c>
-      <c r="Y30" s="2" t="n"/>
-      <c r="Z30" s="2" t="n"/>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">850
+</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3215,19 +4679,20 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16099
+          <t xml:space="preserve">16829
 </t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">11209
 </t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>360</t>
+          <t xml:space="preserve">006
+</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -3238,48 +4703,65 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">437
+</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">866
+          <t xml:space="preserve">806
 </t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">656
 </t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t xml:space="preserve">91
+</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">356
-</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="2" t="n"/>
-      <c r="N31" s="2" t="n"/>
+          <t>4566</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>718</t>
+        </is>
+      </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>420344</t>
+          <t xml:space="preserve">200214
+</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">20
+</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1054
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -3297,19 +4779,19 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3611
+          <t xml:space="preserve">5619
 </t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">346
+          <t xml:space="preserve">3946
 </t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1888
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
@@ -3321,19 +4803,20 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94910
+          <t xml:space="preserve">4418
 </t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t xml:space="preserve">1122
+</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3354,7 +4837,12 @@
 </t>
         </is>
       </c>
-      <c r="D32" s="2" t="n"/>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225
+</t>
+        </is>
+      </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">137
@@ -3375,35 +4863,55 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="n"/>
-      <c r="L32" s="2" t="n"/>
-      <c r="M32" s="2" t="n"/>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="n"/>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">941
+</t>
+        </is>
+      </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -3419,17 +4927,28 @@
 </t>
         </is>
       </c>
-      <c r="S32" s="2" t="n"/>
-      <c r="T32" s="2" t="n"/>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2810
+          <t xml:space="preserve">1163
 </t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>114</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -3438,9 +4957,23 @@
 </t>
         </is>
       </c>
-      <c r="X32" s="2" t="n"/>
-      <c r="Y32" s="2" t="n"/>
-      <c r="Z32" s="2" t="n"/>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">888
+</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>9416</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>21</t>
@@ -3453,75 +4986,106 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n"/>
-      <c r="E33" s="2" t="n"/>
-      <c r="F33" s="2" t="n"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4828
+</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1119
+</t>
+        </is>
+      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="n"/>
-      <c r="M33" s="2" t="n"/>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1149
+</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="n"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="n"/>
+          <t xml:space="preserve">8950
+</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1581</t>
+          <t xml:space="preserve">1198
+</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">9011
 </t>
         </is>
       </c>
@@ -3531,18 +5095,28 @@
 </t>
         </is>
       </c>
-      <c r="V33" s="2" t="n"/>
-      <c r="W33" s="2" t="n"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1166
+</t>
+        </is>
+      </c>
       <c r="X33" s="2" t="n"/>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1950
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -3558,75 +5132,138 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4828
+</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
+          <t xml:space="preserve">1117
 </t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
-</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="n"/>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">949
-</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="n"/>
-      <c r="L34" s="2" t="n"/>
-      <c r="M34" s="2" t="n"/>
-      <c r="N34" s="2" t="n"/>
+          <t xml:space="preserve">49
+</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">930
 </t>
         </is>
       </c>
-      <c r="P34" s="2" t="n"/>
-      <c r="Q34" s="2" t="n"/>
-      <c r="R34" s="2" t="n"/>
-      <c r="S34" s="2" t="n"/>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1219
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
-</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="n"/>
-      <c r="W34" s="2" t="n"/>
+          <t xml:space="preserve">1144
+</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1834
+</t>
+        </is>
+      </c>
       <c r="X34" s="2" t="n"/>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
-</t>
-        </is>
-      </c>
-      <c r="Z34" s="2" t="inlineStr"/>
+          <t xml:space="preserve">718
+</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>23</t>
@@ -3639,62 +5276,147 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="2" t="n"/>
-      <c r="D35" s="2" t="n"/>
-      <c r="E35" s="2" t="n"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4928
+</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1250
+</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11136
+</t>
+        </is>
+      </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">1183
 </t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1294
-</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="n"/>
-      <c r="I35" s="2" t="n"/>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1083
+</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="n"/>
-      <c r="M35" s="2" t="n"/>
-      <c r="N35" s="2" t="n"/>
+          <t xml:space="preserve">080
+</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1116
+</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">920
 </t>
         </is>
       </c>
-      <c r="P35" s="2" t="n"/>
-      <c r="Q35" s="2" t="n"/>
-      <c r="R35" s="2" t="n"/>
-      <c r="S35" s="2" t="n"/>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1600
-</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="n"/>
-      <c r="V35" s="2" t="n"/>
-      <c r="W35" s="2" t="n"/>
-      <c r="X35" s="2" t="n"/>
-      <c r="Y35" s="2" t="n"/>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1167
+</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">892
 </t>
         </is>
       </c>
@@ -3710,23 +5432,47 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n"/>
-      <c r="E36" s="2" t="n"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4983
+</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1136
+</t>
+        </is>
+      </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
-</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="n"/>
-      <c r="I36" s="2" t="n"/>
+          <t xml:space="preserve">2894
+</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">40
@@ -3735,47 +5481,96 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="n"/>
+          <t xml:space="preserve">800
+</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1086
-</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="n"/>
-      <c r="O36" s="2" t="n"/>
+          <t xml:space="preserve">1135
+</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91800
+</t>
+        </is>
+      </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="n"/>
-      <c r="R36" s="2" t="n"/>
-      <c r="S36" s="2" t="n"/>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2188
+</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
-</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="n"/>
+          <t xml:space="preserve">6008
+</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114248
+</t>
+        </is>
+      </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="W36" s="2" t="n"/>
-      <c r="X36" s="2" t="n"/>
-      <c r="Y36" s="2" t="n"/>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1185
+</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">755
+</t>
+        </is>
+      </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -3793,112 +5588,144 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11828
+          <t xml:space="preserve">1983
 </t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
-</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr"/>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">139
+</t>
+        </is>
+      </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9286
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1103
+</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="n"/>
-      <c r="K37" s="2" t="inlineStr"/>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">166
+</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="n"/>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94490
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr"/>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11242
+</t>
+        </is>
+      </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2848
+          <t xml:space="preserve">1710
 </t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3124
+          <t xml:space="preserve">5521
 </t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">1082
 </t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12910
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>504</t>
+          <t xml:space="preserve">159
+</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9092
+          <t xml:space="preserve">798
 </t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1281
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -3916,85 +5743,148 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94386
-</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="n"/>
-      <c r="E38" s="2" t="n"/>
+          <t xml:space="preserve">1228
+</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1242
+</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8258
+</t>
+        </is>
+      </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="n"/>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">040
 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">1108
 </t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="n"/>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1229
+</t>
+        </is>
+      </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>454</t>
+          <t xml:space="preserve">291
+</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="n"/>
+          <t xml:space="preserve">80120
+</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">4490
 </t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="n"/>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1134
+</t>
+        </is>
+      </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="n"/>
-      <c r="T38" s="2" t="n"/>
-      <c r="U38" s="2" t="n"/>
+          <t xml:space="preserve">010
+</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">848
+</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3134
+</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4641</t>
-        </is>
-      </c>
-      <c r="X38" s="2" t="n"/>
-      <c r="Y38" s="2" t="n"/>
-      <c r="Z38" s="2" t="n"/>
+          <t xml:space="preserve">809
+</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">820
+</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9402
+</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1281
+</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -4009,54 +5899,73 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13953
+          <t xml:space="preserve">94386
 </t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="n"/>
-      <c r="K39" s="2" t="n"/>
-      <c r="L39" s="2" t="n"/>
-      <c r="M39" s="2" t="n"/>
-      <c r="N39" s="2" t="n"/>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">232
+</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1151
+</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1521
+</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">898
 </t>
         </is>
       </c>
@@ -4066,36 +5975,66 @@
 </t>
         </is>
       </c>
-      <c r="Q39" s="2" t="n"/>
-      <c r="R39" s="2" t="n"/>
-      <c r="S39" s="2" t="n"/>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">227
+</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5208
+          <t xml:space="preserve">621
 </t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
-</t>
-        </is>
-      </c>
-      <c r="W39" s="2" t="n"/>
-      <c r="X39" s="2" t="n"/>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
-</t>
-        </is>
-      </c>
-      <c r="Z39" s="2" t="n"/>
+          <t xml:space="preserve">2249
+</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 0
+</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>26</t>
@@ -4110,65 +6049,129 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99451
-</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="n"/>
-      <c r="E40" s="2" t="n"/>
+          <t xml:space="preserve">3950
+</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1645
+</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1920
+</t>
+        </is>
+      </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="n"/>
-      <c r="H40" s="2" t="n"/>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1118
+</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">0016
 </t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
-</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="n"/>
-      <c r="L40" s="2" t="n"/>
-      <c r="M40" s="2" t="n"/>
-      <c r="N40" s="2" t="n"/>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11190
+</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="n"/>
-      <c r="Q40" s="2" t="n"/>
-      <c r="R40" s="2" t="n"/>
-      <c r="S40" s="2" t="n"/>
-      <c r="T40" s="2" t="n"/>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1196
+</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">528
+</t>
+        </is>
+      </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
-</t>
-        </is>
-      </c>
-      <c r="W40" s="2" t="n"/>
-      <c r="X40" s="2" t="n"/>
-      <c r="Y40" s="2" t="n"/>
+          <t xml:space="preserve">1710
+</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
@@ -4186,28 +6189,64 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>40344</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="n"/>
+          <t xml:space="preserve">4084
+</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">237
+</t>
+        </is>
+      </c>
       <c r="E41" s="2" t="n"/>
-      <c r="F41" s="2" t="n"/>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
       <c r="G41" s="2" t="n"/>
-      <c r="H41" s="2" t="n"/>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1119
+</t>
+        </is>
+      </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="n"/>
-      <c r="K41" s="2" t="n"/>
-      <c r="L41" s="2" t="n"/>
-      <c r="M41" s="2" t="n"/>
+          <t xml:space="preserve">1111
+</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47
+</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="n"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
@@ -4217,36 +6256,51 @@
 </t>
         </is>
       </c>
-      <c r="Q41" s="2" t="n"/>
-      <c r="R41" s="2" t="n"/>
-      <c r="S41" s="2" t="n"/>
-      <c r="T41" s="2" t="n"/>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">685
+</t>
+        </is>
+      </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">1720
 </t>
         </is>
       </c>
       <c r="X41" s="2" t="n"/>
       <c r="Y41" s="2" t="n"/>
-      <c r="Z41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
+      <c r="Z41" s="2" t="n"/>
       <c r="AA41" t="inlineStr">
         <is>
           <t>28</t>
@@ -4261,44 +6315,64 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3401
+          <t xml:space="preserve">3491
 </t>
         </is>
       </c>
       <c r="D42" s="2" t="n"/>
-      <c r="E42" s="2" t="n"/>
-      <c r="F42" s="2" t="n"/>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="G42" s="2" t="n"/>
-      <c r="H42" s="2" t="n"/>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1137
+</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">40
 </t>
         </is>
       </c>
-      <c r="K42" s="2" t="n"/>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">698
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="n"/>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">889
 </t>
         </is>
       </c>
@@ -4308,17 +6382,42 @@
 </t>
         </is>
       </c>
-      <c r="Q42" s="2" t="n"/>
-      <c r="R42" s="2" t="n"/>
-      <c r="S42" s="2" t="n"/>
-      <c r="T42" s="2" t="n"/>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">434
+</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2895
+</t>
+        </is>
+      </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="n"/>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">168
@@ -4352,55 +6451,127 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13370
-</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="n"/>
-      <c r="E43" s="2" t="n"/>
-      <c r="F43" s="2" t="n"/>
-      <c r="G43" s="2" t="n"/>
-      <c r="H43" s="2" t="n"/>
-      <c r="I43" s="2" t="n"/>
+          <t xml:space="preserve">5170
+</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1101
+</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1114
+</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="n"/>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01
+</t>
+        </is>
+      </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="n"/>
-      <c r="N43" s="2" t="n"/>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="n"/>
-      <c r="Q43" s="2" t="n"/>
-      <c r="R43" s="2" t="n"/>
+          <t xml:space="preserve">820
+</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12229
+</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="n"/>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">520
+</t>
+        </is>
+      </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>1424</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="n"/>
-      <c r="W43" s="2" t="n"/>
-      <c r="X43" s="2" t="n"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">818
@@ -4409,7 +6580,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">987
+          <t xml:space="preserve">37
 </t>
         </is>
       </c>
@@ -4427,12 +6598,22 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16531
-</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="n"/>
-      <c r="E44" s="2" t="n"/>
+          <t xml:space="preserve">6531
+</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">180
@@ -4440,8 +6621,18 @@
         </is>
       </c>
       <c r="G44" s="2" t="n"/>
-      <c r="H44" s="2" t="n"/>
-      <c r="I44" s="2" t="n"/>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">50
@@ -4456,7 +6647,7 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
@@ -4473,47 +6664,47 @@
 </t>
         </is>
       </c>
-      <c r="P44" s="2" t="n"/>
-      <c r="Q44" s="2" t="n"/>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">1681
 </t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9593
-</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1108
-</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="n"/>
+          <t xml:space="preserve">595
+</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="n"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
       <c r="W44" s="2" t="n"/>
       <c r="X44" s="2" t="n"/>
-      <c r="Y44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">780
-</t>
-        </is>
-      </c>
-      <c r="Z44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">850
-</t>
-        </is>
-      </c>
+      <c r="Y44" s="2" t="n"/>
+      <c r="Z44" s="2" t="n"/>
       <c r="AA44" t="inlineStr">
         <is>
           <t>31</t>
@@ -4528,68 +6719,118 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228301
+          <t xml:space="preserve">22830
 </t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1917
-</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="n"/>
-      <c r="F45" s="2" t="n"/>
+          <t xml:space="preserve">1985
+</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2191
+</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1102
+</t>
+        </is>
+      </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">1288
 </t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
-</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="n"/>
-      <c r="M45" s="2" t="n"/>
-      <c r="N45" s="2" t="n"/>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">825
+</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">918
+</t>
+        </is>
+      </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2409
-</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="n"/>
-      <c r="Q45" s="2" t="n"/>
-      <c r="R45" s="2" t="n"/>
+          <t xml:space="preserve">2909
+</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1126
+</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1216
+</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1041
+</t>
+        </is>
+      </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">982
-</t>
-        </is>
-      </c>
-      <c r="T45" s="2" t="n"/>
-      <c r="U45" s="2" t="n"/>
+          <t xml:space="preserve">998
+</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3810
+</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1690
+</t>
+        </is>
+      </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1118
@@ -4598,20 +6839,24 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">958
+          <t xml:space="preserve">2208
 </t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
-</t>
-        </is>
-      </c>
-      <c r="Y45" s="2" t="n"/>
+          <t xml:space="preserve">896
+</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>46484</t>
+        </is>
+      </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
@@ -4629,19 +6874,20 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294970
+          <t xml:space="preserve">4980
 </t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1236
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">133
+</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -4652,44 +6898,70 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44
+</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1138
+</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1389
+</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2541
+</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">228
 </t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>444</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="n"/>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="n"/>
-      <c r="N46" s="2" t="n"/>
-      <c r="O46" s="2" t="n"/>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="n"/>
       <c r="R46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">171
@@ -4702,22 +6974,48 @@
 </t>
         </is>
       </c>
-      <c r="T46" s="2" t="n"/>
-      <c r="U46" s="2" t="n"/>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">585
+</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1142
+</t>
+        </is>
+      </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2126</t>
+          <t xml:space="preserve">186
+</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="X46" s="2" t="n"/>
-      <c r="Y46" s="2" t="n"/>
-      <c r="Z46" s="2" t="n"/>
+          <t xml:space="preserve">1159
+</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1166
+</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">878
+</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/601/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/601/Midpoint_Excel_with_OCR_Results.xlsx
@@ -626,14 +626,13 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5829
+          <t xml:space="preserve">5822
 </t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -662,17 +661,19 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>451</t>
+          <t xml:space="preserve">28
+</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">92
+</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -690,7 +691,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -726,24 +727,20 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1520
-</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t xml:space="preserve">520
+</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr"/>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11207
+          <t xml:space="preserve">10 7 1
 </t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -764,13 +761,13 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2889
+          <t xml:space="preserve">3885
 </t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">2291
 </t>
         </is>
       </c>
@@ -794,7 +791,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1123
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -806,14 +803,13 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -824,13 +820,13 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -842,7 +838,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -858,7 +854,12 @@
 </t>
         </is>
       </c>
-      <c r="S5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">520
@@ -891,7 +892,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">755
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
@@ -933,7 +934,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -969,19 +970,19 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">1309
 </t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
@@ -999,7 +1000,7 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
@@ -1035,13 +1036,13 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -1076,15 +1077,10 @@
 </t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
+      <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11898
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -1096,25 +1092,25 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">1120
 </t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -1126,26 +1122,25 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1236
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1521
 </t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5930
+          <t xml:space="preserve">2930
 </t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr"/>
@@ -1157,7 +1152,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -1169,7 +1164,7 @@
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -1181,7 +1176,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -1193,13 +1188,13 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -1223,7 +1218,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">419
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -1265,8 +1260,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1283,13 +1277,13 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
@@ -1313,7 +1307,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -1325,7 +1319,7 @@
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">358
 </t>
         </is>
       </c>
@@ -1370,7 +1364,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">616
+          <t xml:space="preserve">656
 </t>
         </is>
       </c>
@@ -1382,56 +1376,49 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8815
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">651
-</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">631
+</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">511
 </t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">734
 </t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">607
+          <t xml:space="preserve">689
 </t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9590
-</t>
+          <t>15901</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1442,7 +1429,7 @@
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11940
+          <t xml:space="preserve">1140
 </t>
         </is>
       </c>
@@ -1454,32 +1441,27 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1862
-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5776</t>
+          <t xml:space="preserve">126
+</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1530
-</t>
+          <t>530</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15940
-</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>7581</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1941
+</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr"/>
       <c r="X9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">175
@@ -1511,71 +1493,76 @@
         </is>
       </c>
       <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">511
-</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1916
-</t>
-        </is>
-      </c>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">829
+</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">151
+</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">11
 </t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t xml:space="preserve">88
+</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1209
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">9230
 </t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1081
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -1587,13 +1574,13 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">068
+          <t xml:space="preserve">868
 </t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21626
+          <t xml:space="preserve">2126
 </t>
         </is>
       </c>
@@ -1605,13 +1592,13 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9590
+          <t xml:space="preserve">940
 </t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0098
+          <t xml:space="preserve">808
 </t>
         </is>
       </c>
@@ -1623,13 +1610,13 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4198
+          <t xml:space="preserve">8481
 </t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
@@ -1647,7 +1634,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4490
+          <t xml:space="preserve">4950
 </t>
         </is>
       </c>
@@ -1665,7 +1652,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
@@ -1683,13 +1670,13 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -1714,20 +1701,19 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">9218
 </t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">11 3 8
 </t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12218
-</t>
+          <t>418</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
@@ -1738,13 +1724,13 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">1782
 </t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">629
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
@@ -1793,8 +1779,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2218
-</t>
+          <t>9242</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1805,126 +1790,106 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1181
+</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">181
 </t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1108
-</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
+          <t>8850</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2104
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t xml:space="preserve">820
+</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1157
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">163
+</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr"/>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">340
 </t>
         </is>
       </c>
@@ -1972,7 +1937,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">991
 </t>
         </is>
       </c>
@@ -2002,13 +1967,13 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1835
+          <t xml:space="preserve">1385
 </t>
         </is>
       </c>
@@ -2020,7 +1985,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -2062,7 +2027,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -2080,7 +2045,7 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2408
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -2117,18 +2082,19 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>281</t>
+          <t xml:space="preserve">98
+</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
@@ -2152,7 +2118,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
@@ -2174,11 +2140,7 @@
 </t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
+      <c r="P14" s="2" t="inlineStr"/>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1158
@@ -2193,13 +2155,13 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">905
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -2218,13 +2180,13 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
@@ -2255,14 +2217,13 @@
       <c r="D15" s="2" t="n"/>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">0134
 </t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2273,25 +2234,24 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>715</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1214
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">868
 </t>
         </is>
       </c>
@@ -2309,8 +2269,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -2327,8 +2286,7 @@
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
@@ -2339,13 +2297,13 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">719
+          <t xml:space="preserve">715
 </t>
         </is>
       </c>
@@ -2357,7 +2315,7 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -2412,12 +2370,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
@@ -2435,7 +2393,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">18 2
 </t>
         </is>
       </c>
@@ -2453,7 +2411,8 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t xml:space="preserve">138
+</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2470,7 +2429,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -2543,7 +2502,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19722
+          <t xml:space="preserve">19732
 </t>
         </is>
       </c>
@@ -2555,33 +2514,28 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>274</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">911
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">474
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6494
-</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">59
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">644
+</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">69
@@ -2590,13 +2544,13 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
+          <t xml:space="preserve">460
 </t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1912
+          <t xml:space="preserve">732
 </t>
         </is>
       </c>
@@ -2608,43 +2562,39 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11642</t>
+          <t>154</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">648
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">969
+          <t xml:space="preserve">069
 </t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">838
-</t>
+          <t>614</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">884
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1648
-</t>
+          <t>39452</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2655,13 +2605,13 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">845
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1806
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -2673,7 +2623,7 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4888
+          <t xml:space="preserve">4288
 </t>
         </is>
       </c>
@@ -2697,8 +2647,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2250
-</t>
+          <t>14694</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2709,18 +2658,18 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">138
+</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1418
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
@@ -2738,7 +2687,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4214
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
@@ -2757,31 +2706,31 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">929
+</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">198
 </t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">929
-</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -2793,13 +2742,13 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">789
 </t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -2853,13 +2802,13 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -2871,8 +2820,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2883,7 +2831,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -2895,80 +2843,84 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">691
+</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">80
 </t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">691
-</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr"/>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">1170
 </t>
         </is>
       </c>
@@ -2980,7 +2932,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -2998,13 +2950,14 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8406
+          <t xml:space="preserve">4406
 </t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">220
+</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -3021,20 +2974,19 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -3063,8 +3015,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>464</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -3081,7 +3032,7 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -3105,20 +3056,19 @@
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
-</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1198
-</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr"/>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr"/>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">11853
 </t>
         </is>
       </c>
@@ -3130,7 +3080,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">1274
 </t>
         </is>
       </c>
@@ -3166,13 +3116,13 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -3184,7 +3134,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -3227,44 +3177,38 @@
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">876
+</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">768
+</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr"/>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">176
 </t>
         </is>
       </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">768
-</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>755</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
@@ -3305,7 +3249,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -3317,31 +3261,31 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1419
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -3353,7 +3297,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">1562
 </t>
         </is>
       </c>
@@ -3365,8 +3309,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -3383,7 +3326,7 @@
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
@@ -3395,8 +3338,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>0431</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -3407,13 +3349,13 @@
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6 8
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">4182
 </t>
         </is>
       </c>
@@ -3467,7 +3409,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1944
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -3479,13 +3421,13 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4134
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
@@ -3495,12 +3437,7 @@
 </t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">05
-</t>
-        </is>
-      </c>
+      <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">30
@@ -3509,7 +3446,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -3521,13 +3458,13 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">1689
 </t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -3557,7 +3494,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
+          <t xml:space="preserve">7408
 </t>
         </is>
       </c>
@@ -3569,7 +3506,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -3593,7 +3530,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -3611,38 +3548,35 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19212
-</t>
+          <t>4774</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111531
+          <t xml:space="preserve">1131
 </t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">494
+          <t xml:space="preserve">894
 </t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9408
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">431
-</t>
+          <t>26540</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">698
-</t>
+          <t>6364</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3653,7 +3587,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -3665,25 +3599,19 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1221
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1614
+</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8164
-</t>
+          <t>316</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3700,13 +3628,12 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
@@ -3724,32 +3651,30 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9189
+          <t xml:space="preserve">9198
 </t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
+          <t xml:space="preserve">839
 </t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9118
-</t>
+          <t>9421</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">484
+          <t xml:space="preserve">1488
 </t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3810,8 +3735,7 @@
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>459</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -3822,7 +3746,7 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3857,7 +3781,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">695
+          <t xml:space="preserve">696
 </t>
         </is>
       </c>
@@ -3875,13 +3799,13 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -3911,25 +3835,25 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4904
+          <t xml:space="preserve">1304
 </t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2126
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11211
+          <t xml:space="preserve">1931
 </t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -3941,7 +3865,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2128
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -3953,32 +3877,31 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18492
+          <t xml:space="preserve">1342
 </t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -3995,25 +3918,25 @@
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">1729
 </t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">1176
 </t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
+          <t xml:space="preserve">681
 </t>
         </is>
       </c>
@@ -4025,22 +3948,16 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
-</t>
-        </is>
-      </c>
-      <c r="X26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr"/>
       <c r="Y26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">940
@@ -4067,7 +3984,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2260
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
@@ -4079,8 +3996,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>46431</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -4097,26 +4013,21 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 5
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1846
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
@@ -4138,15 +4049,10 @@
 </t>
         </is>
       </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
+      <c r="P27" s="2" t="inlineStr"/>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
@@ -4176,32 +4082,30 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4218,7 +4122,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2878
+          <t xml:space="preserve">878
 </t>
         </is>
       </c>
@@ -4236,8 +4140,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -4254,13 +4157,12 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -4272,7 +4174,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
@@ -4284,7 +4186,7 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -4314,13 +4216,13 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">710
 </t>
         </is>
       </c>
@@ -4338,7 +4240,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -4374,7 +4276,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20239
+          <t xml:space="preserve">3059
 </t>
         </is>
       </c>
@@ -4392,8 +4294,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11179
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -4404,34 +4305,29 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1654
-</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">147
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">142
@@ -4440,7 +4336,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -4451,7 +4347,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -4481,7 +4377,7 @@
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>66</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
@@ -4546,14 +4442,13 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>845</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -4571,25 +4466,25 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">67
 </t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">844
 </t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -4601,8 +4496,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4625,7 +4519,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">700
+          <t xml:space="preserve">709
 </t>
         </is>
       </c>
@@ -4679,19 +4573,19 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16829
+          <t xml:space="preserve">16899
 </t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11209
+          <t xml:space="preserve">11298
 </t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">006
+          <t xml:space="preserve">606
 </t>
         </is>
       </c>
@@ -4715,7 +4609,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">656
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -4727,7 +4621,8 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>4566</t>
+          <t xml:space="preserve">386
+</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -4738,36 +4633,31 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>718</t>
-        </is>
-      </c>
+          <t xml:space="preserve">117
+</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200214
+          <t xml:space="preserve">4798
 </t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
@@ -4779,7 +4669,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5619
+          <t xml:space="preserve">5618
 </t>
         </is>
       </c>
@@ -4789,33 +4679,28 @@
 </t>
         </is>
       </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="V31" s="2" t="inlineStr"/>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">811
+</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">880
 </t>
         </is>
       </c>
-      <c r="W31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">811
-</t>
-        </is>
-      </c>
-      <c r="X31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4418
+          <t xml:space="preserve">4 16 8
 </t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -4839,7 +4724,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -4863,7 +4748,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -4875,16 +4760,11 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1 8
+</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">149
@@ -4893,13 +4773,13 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -4935,13 +4815,12 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>1163</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -4965,13 +4844,13 @@
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">883
 </t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>9416</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4988,7 +4867,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4828
+          <t xml:space="preserve">4818
 </t>
         </is>
       </c>
@@ -5000,19 +4879,19 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">1719
 </t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5022,58 +4901,52 @@
 </t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
+      <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
-</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="N33" s="2" t="n"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8950
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">1158
 </t>
         </is>
       </c>
@@ -5085,7 +4958,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9011
+          <t xml:space="preserve">901
 </t>
         </is>
       </c>
@@ -5097,13 +4970,13 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
@@ -5134,43 +5007,43 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4828
+          <t xml:space="preserve">4228
 </t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">2491
 </t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>115</t>
+          <t xml:space="preserve">66184 5
+</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1117
+          <t xml:space="preserve">1917
 </t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -5180,11 +5053,7 @@
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+      <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">130
@@ -5193,7 +5062,7 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">1924
 </t>
         </is>
       </c>
@@ -5203,12 +5072,7 @@
 </t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
+      <c r="P34" s="2" t="inlineStr"/>
       <c r="Q34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">238
@@ -5223,19 +5087,19 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">3195
 </t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -5247,14 +5111,14 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1834
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
       <c r="X34" s="2" t="n"/>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
+          <t xml:space="preserve">710
 </t>
         </is>
       </c>
@@ -5284,19 +5148,18 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1250
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11136
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1183
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -5308,25 +5171,24 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1083
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5338,13 +5200,13 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">1916
 </t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">811
 </t>
         </is>
       </c>
@@ -5356,7 +5218,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5368,7 +5230,7 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -5380,7 +5242,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">568
 </t>
         </is>
       </c>
@@ -5398,16 +5260,11 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="X35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1167
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr"/>
       <c r="Y35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">210
@@ -5416,7 +5273,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
@@ -5440,7 +5297,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">2180
 </t>
         </is>
       </c>
@@ -5452,8 +5309,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -5481,7 +5337,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -5493,72 +5349,73 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1135
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">900
+</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600
+</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">17
 </t>
         </is>
       </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">91800
-</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2188
-</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6008
-</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114248
-</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="W36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -5588,8 +5445,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1983
-</t>
+          <t>994</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -5606,24 +5462,20 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">1921
 </t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
-</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -5653,7 +5505,7 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1811
 </t>
         </is>
       </c>
@@ -5671,7 +5523,7 @@
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11242
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -5683,22 +5535,17 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1710
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521
-</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1082
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">551
+</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">184
@@ -5743,86 +5590,79 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">1281
 </t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8258
+          <t xml:space="preserve">698
 </t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">040
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">1106
 </t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80120
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">831
+</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4490
-</t>
+          <t>449303</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5833,13 +5673,13 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -5851,13 +5691,13 @@
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
@@ -5869,22 +5709,16 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9402
-</t>
-        </is>
-      </c>
-      <c r="Z38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1281
-</t>
-        </is>
-      </c>
+          <t>412524</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr"/>
       <c r="AA38" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -5899,7 +5733,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94386
+          <t xml:space="preserve">4386
 </t>
         </is>
       </c>
@@ -5923,31 +5757,36 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>185</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr"/>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
@@ -5959,19 +5798,18 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1521
+          <t xml:space="preserve">1581
 </t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
-</t>
+          <t>898</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5989,14 +5827,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>4805</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">621
-</t>
+          <t>639</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -6013,7 +5849,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
@@ -6025,13 +5861,13 @@
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2249
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 0
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -6049,19 +5885,19 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3950
+          <t xml:space="preserve">23923
 </t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1645
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
@@ -6073,36 +5909,41 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
-</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1119
+</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0016
-</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">806
+</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11190
-</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1112
+</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">910
@@ -6117,7 +5958,7 @@
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
+          <t xml:space="preserve">296
 </t>
         </is>
       </c>
@@ -6129,31 +5970,31 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">528
+          <t xml:space="preserve">520
 </t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1710
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -6165,13 +6006,13 @@
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">710
 </t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -6202,7 +6043,7 @@
       <c r="E41" s="2" t="n"/>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
@@ -6215,7 +6056,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
+          <t xml:space="preserve">9810
 </t>
         </is>
       </c>
@@ -6239,14 +6080,14 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="N41" s="2" t="n"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
@@ -6276,7 +6117,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">685
+          <t xml:space="preserve">588
 </t>
         </is>
       </c>
@@ -6288,13 +6129,13 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1720
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -6315,14 +6156,14 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3491
+          <t xml:space="preserve">3401
 </t>
         </is>
       </c>
       <c r="D42" s="2" t="n"/>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
@@ -6335,11 +6176,16 @@
       <c r="G42" s="2" t="n"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
-</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr"/>
+          <t xml:space="preserve">137
+</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">40
@@ -6354,13 +6200,13 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -6384,13 +6230,13 @@
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">434
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -6402,7 +6248,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2895
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
@@ -6451,13 +6297,13 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5170
+          <t xml:space="preserve">5370
 </t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>495</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
@@ -6467,34 +6313,28 @@
 </t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1101
-</t>
-        </is>
-      </c>
+      <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -6505,18 +6345,19 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">151
+</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -6528,13 +6369,13 @@
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12229
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -6546,13 +6387,13 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">112
+</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
@@ -6563,7 +6404,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
@@ -6598,7 +6439,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6531
+          <t xml:space="preserve">2231
 </t>
         </is>
       </c>
@@ -6647,8 +6488,7 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -6666,7 +6506,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -6678,7 +6518,7 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1681
+          <t xml:space="preserve">1671
 </t>
         </is>
       </c>
@@ -6697,7 +6537,7 @@
       <c r="U44" s="2" t="n"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">2181
 </t>
         </is>
       </c>
@@ -6719,144 +6559,144 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22830
+          <t xml:space="preserve">22820
 </t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1985
+          <t xml:space="preserve">19818
 </t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2191
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
+          <t xml:space="preserve">1108
 </t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">620
 </t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1288
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">2862
 </t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1801
 </t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">825
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">070
 </t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">313
 </t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2909
+          <t xml:space="preserve">2409
 </t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1041
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3810
+          <t xml:space="preserve">3310
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1690
+          <t xml:space="preserve">1620
 </t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2208
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
-</t>
+          <t>360</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>46484</t>
+          <t xml:space="preserve">9668
+</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -6874,7 +6714,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4980
+          <t xml:space="preserve">4970
 </t>
         </is>
       </c>
@@ -6886,7 +6726,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -6920,12 +6760,7 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
+      <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">149
@@ -6934,25 +6769,25 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1389
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2541
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -6980,12 +6815,7 @@
 </t>
         </is>
       </c>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1142
-</t>
-        </is>
-      </c>
+      <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">186
@@ -6994,19 +6824,19 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
+          <t xml:space="preserve">778
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/601/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/601/Midpoint_Excel_with_OCR_Results.xlsx
@@ -626,13 +626,14 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5822
+          <t xml:space="preserve">585
 </t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t xml:space="preserve">251
+</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -667,19 +668,19 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
@@ -691,7 +692,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">1295
 </t>
         </is>
       </c>
@@ -727,23 +728,23 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
-</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr"/>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">151
+</t>
+        </is>
+      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10 7 1
-</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">9187
+</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr"/>
       <c r="X4" s="2" t="n"/>
       <c r="Y4" s="2" t="n"/>
       <c r="Z4" s="2" t="n"/>
@@ -761,13 +762,13 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3885
+          <t xml:space="preserve">388
 </t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2291
+          <t xml:space="preserve">2939
 </t>
         </is>
       </c>
@@ -791,54 +792,55 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1128
+</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1535
+</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">121
 </t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">135
-</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">999
 </t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -850,13 +852,13 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -868,7 +870,7 @@
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -892,7 +894,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">755
 </t>
         </is>
       </c>
@@ -916,7 +918,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5089
+          <t xml:space="preserve">508
 </t>
         </is>
       </c>
@@ -928,26 +930,25 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">2128
 </t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -964,7 +965,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -976,19 +977,19 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1309
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">451
 </t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -1018,7 +1019,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">619
+          <t xml:space="preserve">615
 </t>
         </is>
       </c>
@@ -1042,17 +1043,21 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
-        </is>
-      </c>
-      <c r="Z6" s="2" t="n"/>
+          <t xml:space="preserve">270
+</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>3</t>
@@ -1077,10 +1082,15 @@
 </t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -1092,13 +1102,13 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -1110,7 +1120,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
@@ -1128,31 +1138,37 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1521
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2930
+          <t xml:space="preserve">524
 </t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr"/>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225
+</t>
+        </is>
+      </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -1170,13 +1186,13 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
@@ -1188,13 +1204,13 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">825
 </t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -1218,7 +1234,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -1248,96 +1264,111 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">151
+</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">205
+</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">151
-</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">930
-</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">205
-</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">175
-</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
+          <t xml:space="preserve">640
 </t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">358
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">1114
 </t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1168
+</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">160
 </t>
         </is>
       </c>
-      <c r="X8" s="2" t="n"/>
-      <c r="Y8" s="2" t="n"/>
-      <c r="Z8" s="2" t="n"/>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>5</t>
@@ -1352,19 +1383,19 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22249
+          <t xml:space="preserve">2224
 </t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
+          <t xml:space="preserve">11185
 </t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">656
+          <t xml:space="preserve">676
 </t>
         </is>
       </c>
@@ -1376,7 +1407,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
@@ -1386,10 +1417,14 @@
 </t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>7064</t>
+        </is>
+      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1406,19 +1441,20 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
+          <t xml:space="preserve">002
 </t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">1664
 </t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15901</t>
+          <t xml:space="preserve">590
+</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1441,45 +1477,47 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>77</t>
+          <t xml:space="preserve">862
+</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">2126
 </t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>530</t>
+          <t xml:space="preserve">230
+</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1941
-</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1151
+</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
-        </is>
-      </c>
-      <c r="Z9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">940
+</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1492,131 +1530,142 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">445
+</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">237
+</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">135
+</t>
+        </is>
+      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">97 9
+</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">33
+</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9230
+          <t xml:space="preserve">998
 </t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">801
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2126
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">897
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8481
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -1634,137 +1683,144 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4950
-</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">889
+</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1406491
+</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11812 1
+</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02 4
+</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">38
 </t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">147
-</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9218
-</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11 3 8
-</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>418</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1782
-</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">628
-</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="X11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="Y11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">830
-</t>
-        </is>
-      </c>
-      <c r="Z11" s="2" t="n"/>
       <c r="AA11" t="inlineStr">
         <is>
           <t>6</t>
@@ -1779,123 +1835,132 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9242</t>
+          <t xml:space="preserve">2295
+</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
+          <t xml:space="preserve">91
+</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1130
+</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1143
+</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1839
+</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9318
+</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">12
 </t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>8850</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1177
 </t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
+          <t>551</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr"/>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
-</t>
+          <t>9405</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -1913,143 +1978,148 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2290
+          <t xml:space="preserve">3220
 </t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">991
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1385
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">1158
 </t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">745
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="Z13" s="2" t="n"/>
+          <t xml:space="preserve">850
+</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>8</t>
@@ -2064,43 +2134,43 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3220
+          <t xml:space="preserve">3240
 </t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -2112,87 +2182,97 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
+          <t xml:space="preserve">568
 </t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">945
-</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr"/>
+          <t xml:space="preserve">001
+</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">1158
 </t>
         </is>
       </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">205
-</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="n"/>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">719
 </t>
         </is>
       </c>
@@ -2210,106 +2290,115 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3240
-</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n"/>
+          <t xml:space="preserve">3079
+</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0134
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>114</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t xml:space="preserve">136
+</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>154</t>
+          <t xml:space="preserve">155
+</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">0911
 </t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t xml:space="preserve">198
+</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">715
+          <t xml:space="preserve">730
 </t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
@@ -2321,25 +2410,25 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
@@ -2357,137 +2446,143 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3079
-</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n"/>
+          <t xml:space="preserve">1475
+</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1148
+</t>
+        </is>
+      </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>6747</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t xml:space="preserve">92
+</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">874
 </t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1644
 </t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18 2
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">468
 </t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">732
 </t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>6341</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">11404
 </t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>965</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>881</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
+          <t xml:space="preserve">3945
 </t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">843
 </t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
+          <t xml:space="preserve">786
 </t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">851
 </t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">875
-</t>
-        </is>
-      </c>
-      <c r="Z16" s="2" t="n"/>
+          <t xml:space="preserve">12088
+</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2502,135 +2597,145 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19732
+          <t xml:space="preserve">2950
 </t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>274</t>
+          <t xml:space="preserve">115
+</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">088
 </t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">644
-</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr"/>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">28 14
 </t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">460
+          <t xml:space="preserve">2695
 </t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">732
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>154</t>
+          <t xml:space="preserve">181
+</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">118
+</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t xml:space="preserve">112
+</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">069
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t xml:space="preserve">167
+</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39452</t>
+          <t xml:space="preserve">929
+</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">851
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4288
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2647,138 +2752,134 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14694</t>
+          <t xml:space="preserve">4283
+</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">187
+</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>484</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">1109
 </t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr"/>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">1130
 </t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
-</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">789
-</t>
+          <t>691</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">1701
 </t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -2796,143 +2897,145 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4288
+          <t xml:space="preserve">4406
 </t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5140
+</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1151
+</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2149
+</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">181
 </t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>645</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">691
+          <t xml:space="preserve">540
 </t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">1870
 </t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -2950,137 +3053,143 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4406
+          <t xml:space="preserve">1531
 </t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">14
 </t>
         </is>
       </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>464</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">205
+</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">768
+</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1176
+</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">920
 </t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">540
-</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr"/>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="X20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11853
-</t>
-        </is>
-      </c>
-      <c r="Y20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">810
-</t>
-        </is>
-      </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1274
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -3098,134 +3207,145 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531
+          <t xml:space="preserve">2617
 </t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr"/>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">998
 </t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">876
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">740
+</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">185
 </t>
         </is>
       </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">768
-</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr"/>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>755</t>
+          <t xml:space="preserve">170
+</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -3243,143 +3363,144 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2617
+          <t xml:space="preserve">1233
 </t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">111
 </t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">918
+</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">740
+</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>9470</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1562
-</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1213</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">908
-</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">214
-</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0431</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">740
-</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4182
-</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="X22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="Y22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8809
-</t>
-        </is>
-      </c>
-      <c r="Z22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -3397,140 +3518,135 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233
-</t>
+          <t>1772</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">1131
 </t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">294
 </t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
+          <t xml:space="preserve">943
 </t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+          <t xml:space="preserve">612
+</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1689
-</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">70
 </t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">1090
 </t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7408
+          <t xml:space="preserve">3479
 </t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">406
 </t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">919
 </t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>811</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">945
+          <t xml:space="preserve">9295
 </t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
@@ -3548,133 +3664,146 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t xml:space="preserve">2154
+</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1131
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>26540</t>
+          <t xml:space="preserve">87
+</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6364</t>
+          <t xml:space="preserve">129
+</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">382
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1614
-</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10434
+</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>316</t>
+          <t xml:space="preserve">14
+</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">2211
+</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1090
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t xml:space="preserve">178
+</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3479
+          <t xml:space="preserve">696
 </t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">406
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9198
+          <t xml:space="preserve">1183
 </t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>9421</t>
+          <t xml:space="preserve">183
+</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1488
+          <t xml:space="preserve">871
 </t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>138</t>
+          <t xml:space="preserve">28
+</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3691,7 +3820,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2154
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -3703,121 +3832,121 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1183
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr"/>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">59
+</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">131
+</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1842
+</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">15
 </t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>459</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
-</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">915
+</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr"/>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>478</t>
+          <t xml:space="preserve">1174
+</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">696
-</t>
+          <t>495</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">871
+          <t xml:space="preserve">940
 </t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -3835,31 +3964,31 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1304
+          <t xml:space="preserve">326
 </t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1931
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
@@ -3871,102 +4000,109 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">1846
 </t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1342
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">115
+</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9108
+          <t xml:space="preserve">950
 </t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1729
+          <t xml:space="preserve">2088
 </t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">681
+          <t xml:space="preserve">730
 </t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t xml:space="preserve">179
+</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="X26" s="2" t="inlineStr"/>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1180
+</t>
+        </is>
+      </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -3984,128 +4120,141 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>46431</t>
+          <t xml:space="preserve">1144
+</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr"/>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">1154
 </t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
-</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr"/>
+          <t xml:space="preserve">940
+</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">2108
 </t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7170
+</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">178
 </t>
         </is>
       </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">730
-</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t xml:space="preserve">910
+</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">20
+</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4122,143 +4271,144 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>141</t>
+          <t xml:space="preserve">179
+</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">09
+</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">1154
 </t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1142
+</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">950
+</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">728
+</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">148
 </t>
         </is>
       </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">940
-</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">710
-</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">56
-</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
+      <c r="X28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">158
 </t>
         </is>
       </c>
-      <c r="X28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">838
 </t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">2898
 </t>
         </is>
       </c>
@@ -4276,13 +4426,13 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3059
+          <t xml:space="preserve">2898
 </t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -4294,49 +4444,56 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>119</t>
+          <t xml:space="preserve">175
+</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr"/>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1149
+</t>
+        </is>
+      </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">111
+</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -4353,54 +4510,55 @@
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">728
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t xml:space="preserve">78
+</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">1821
 </t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">838
+          <t xml:space="preserve">850
 </t>
         </is>
       </c>
@@ -4424,138 +4582,132 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2898
+          <t xml:space="preserve">16099
 </t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">11298
+</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">906
 </t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>497</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr"/>
+          <t xml:space="preserve">866
+</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
-</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1149
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">386
+</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">844
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>51</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">1052
 </t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">874
 </t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">901
 </t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">709
+          <t xml:space="preserve">5610
 </t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">345
 </t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">811
 </t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
+          <t xml:space="preserve">4410
 </t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -4573,134 +4725,135 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16899
+          <t xml:space="preserve">3220
 </t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11298
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">606
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">437
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">806
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">386
-</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr"/>
+          <t xml:space="preserve">147
+</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4798
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>1052</t>
+          <t xml:space="preserve">210
+</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5618
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3946
-</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr"/>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4 16 8
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">2144
 </t>
         </is>
       </c>
@@ -4718,139 +4871,139 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3220
-</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+          <t xml:space="preserve">235
+</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>1051</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1128
+</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">830
+</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">900
+</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">22
 </t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">282
-</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 8
-</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">161
-</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">941
-</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">175
-</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>1163</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">883
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">8
+</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4867,129 +5020,145 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4818
+          <t xml:space="preserve">14828
 </t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1719
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1826
+</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">865
 </t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="n"/>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1848
+</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
-        </is>
-      </c>
-      <c r="X33" s="2" t="n"/>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1160
+</t>
+        </is>
+      </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">710
 </t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -5007,99 +5176,114 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4228
+          <t xml:space="preserve">4828
 </t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2491
+          <t xml:space="preserve">1441
 </t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66184 5
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1917
+          <t xml:space="preserve">1126
 </t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">11095
 </t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">25
+</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
-</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="2" t="inlineStr"/>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1924
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
-</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr"/>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">168
 </t>
         </is>
       </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3195
+          <t xml:space="preserve">568
 </t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -5111,23 +5295,23 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
-</t>
-        </is>
-      </c>
-      <c r="X34" s="2" t="n"/>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
-</t>
-        </is>
-      </c>
-      <c r="Z34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="n"/>
       <c r="AA34" t="inlineStr">
         <is>
           <t>23</t>
@@ -5142,7 +5326,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4928
+          <t xml:space="preserve">94928
 </t>
         </is>
       </c>
@@ -5154,36 +5338,36 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t xml:space="preserve">1136
+</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>72793</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>446</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">40
+</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -5194,86 +5378,91 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1916
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">9100
 </t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">2945
 </t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
+          <t xml:space="preserve">6008
 </t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="X35" s="2" t="inlineStr"/>
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1828
+</t>
+        </is>
+      </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">1255
 </t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -5291,41 +5480,43 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4983
+          <t xml:space="preserve">94989
 </t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2180
+          <t xml:space="preserve">2942
 </t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1136
+          <t xml:space="preserve">1139
 </t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">191
+</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2894
+          <t xml:space="preserve">14103
 </t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">127
+</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -5337,97 +5528,97 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">1866
 </t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">1881
 </t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">600
+          <t xml:space="preserve">521
 </t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">1666
 </t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">755
+          <t xml:space="preserve">798
 </t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -5445,135 +5636,137 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t xml:space="preserve">21928
+</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>6657</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1921
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">533
 </t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">1106
 </t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">757
 </t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">7112
 </t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1811
+          <t xml:space="preserve">716
 </t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
+          <t>44203</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1134
+</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810
+</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">848
+</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3134
+</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2348
+</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">910
 </t>
         </is>
       </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292
-</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">551
-</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr"/>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">804
 </t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
+          <t xml:space="preserve">4098
 </t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
+          <t>884</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5590,135 +5783,142 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1281
+          <t xml:space="preserve">438
 </t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">139
+</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">121
 </t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">698
-</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">926
-</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1106
-</t>
-        </is>
-      </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1218
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="n"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">831
-</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>1513</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>449303</t>
+          <t xml:space="preserve">152
+</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3134
+          <t xml:space="preserve">827
 </t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">809
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>412524</t>
-        </is>
-      </c>
-      <c r="Z38" s="2" t="inlineStr"/>
+          <t xml:space="preserve">819
+</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">898
+</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -5733,78 +5933,74 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4386
+          <t xml:space="preserve">395953
 </t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>185</t>
+          <t xml:space="preserve">115
+</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">8115
 </t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1581
+          <t xml:space="preserve">016
 </t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>940</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5815,60 +6011,54 @@
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>4805</t>
+          <t xml:space="preserve">1209
+</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t xml:space="preserve">520
+</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="V39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr"/>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">0158
 </t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>641</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5885,134 +6075,142 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23923
-</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">293
+</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">128
 </t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1230
-</t>
-        </is>
-      </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">115
+</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">008
+</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1190
+</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">890
+</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">588
+</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">120
 </t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">806
-</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr"/>
-      <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1112
-</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">296
-</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">520
-</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -6036,33 +6234,43 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="n"/>
+          <t xml:space="preserve">1237
+</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="n"/>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">1108
 </t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9810
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -6080,14 +6288,19 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="n"/>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">889
 </t>
         </is>
       </c>
@@ -6099,49 +6312,64 @@
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">588
+          <t xml:space="preserve">622
 </t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">120
 </t>
         </is>
       </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="W41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="X41" s="2" t="n"/>
-      <c r="Y41" s="2" t="n"/>
-      <c r="Z41" s="2" t="n"/>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1188
+</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">828
+</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>28</t>
@@ -6160,41 +6388,51 @@
 </t>
         </is>
       </c>
-      <c r="D42" s="2" t="n"/>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="n"/>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
@@ -6206,19 +6444,19 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
@@ -6230,13 +6468,13 @@
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -6248,7 +6486,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">605
 </t>
         </is>
       </c>
@@ -6260,26 +6498,31 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="X42" s="2" t="n"/>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">010
 </t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">3310
 </t>
         </is>
       </c>
@@ -6297,44 +6540,56 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5370
+          <t xml:space="preserve">5571
 </t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>495</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr"/>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">181
 </t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1101
+</t>
+        </is>
+      </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">1996
 </t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>07</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -6351,77 +6606,79 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t xml:space="preserve">580
+</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">192
+</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">1354
 </t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -6439,112 +6696,143 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2231
+          <t xml:space="preserve">2221
 </t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1194
+</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1226
+</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50
+</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1836
+</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">126
 </t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="n"/>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1867
+</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">593
+</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">820
+</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">50
 </t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="n"/>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1671
-</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">595
-</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="n"/>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2181
-</t>
-        </is>
-      </c>
-      <c r="W44" s="2" t="n"/>
-      <c r="X44" s="2" t="n"/>
-      <c r="Y44" s="2" t="n"/>
-      <c r="Z44" s="2" t="n"/>
       <c r="AA44" t="inlineStr">
         <is>
           <t>31</t>
@@ -6559,25 +6847,25 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22820
+          <t xml:space="preserve">29830
 </t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19818
+          <t xml:space="preserve">1417
 </t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">1911
 </t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
@@ -6589,7 +6877,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -6601,37 +6889,37 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2862
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1801
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
+          <t xml:space="preserve">894
 </t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">070
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2409
+          <t xml:space="preserve">53409
 </t>
         </is>
       </c>
@@ -6643,60 +6931,61 @@
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">1024
 </t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">975
 </t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3310
+          <t xml:space="preserve">3510
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1620
+          <t xml:space="preserve">690
 </t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">11115
 </t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">955
 </t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>360</t>
+          <t xml:space="preserve">996
+</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9668
+          <t xml:space="preserve">4668
 </t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
@@ -6726,7 +7015,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -6760,7 +7049,12 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">149
@@ -6769,19 +7063,19 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">006
 </t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">901
 </t>
         </is>
       </c>
@@ -6793,7 +7087,7 @@
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">9228
 </t>
         </is>
       </c>
@@ -6815,10 +7109,15 @@
 </t>
         </is>
       </c>
-      <c r="U46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">115
+</t>
+        </is>
+      </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
@@ -6830,19 +7129,19 @@
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">778
+          <t xml:space="preserve">1120
 </t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/601/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/601/Midpoint_Excel_with_OCR_Results.xlsx
@@ -626,122 +626,102 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">585
-</t>
+          <t>585</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1295
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9187
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr"/>
@@ -762,146 +742,122 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">388
-</t>
+          <t>3883</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2939
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1535
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">999
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
-</t>
+          <t>520</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">755
-</t>
+          <t>755</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -918,32 +874,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">508
-</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -953,104 +904,87 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">451
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>299</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">615
-</t>
+          <t>615</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1072,146 +1006,122 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5129
-</t>
+          <t>5129</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">524
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">591
-</t>
+          <t>591</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">825
-</t>
+          <t>825</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1228,68 +1138,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2298
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>299</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1299,74 +1198,62 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">640
-</t>
+          <t>640</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>760</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1383,38 +1270,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2224
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11185
-</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">676
-</t>
+          <t>676</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">931
-</t>
+          <t>931</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>509</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">631
-</t>
+          <t>631</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1429,92 +1310,77 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">511
-</t>
+          <t>511</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">734
-</t>
+          <t>734</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">002
-</t>
+          <t>602</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1664
-</t>
+          <t>664</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
-</t>
+          <t>590</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
-</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
-</t>
+          <t>881</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>862</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>530</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
-</t>
+          <t>940</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr"/>
@@ -1532,141 +1398,118 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">445
-</t>
+          <t>4450</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97 9
-</t>
+          <t>9 21</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
-</t>
+          <t>918</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
+          <t>830</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1688,26 +1531,22 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1717,44 +1556,37 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
-</t>
+          <t>880</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1764,63 +1596,34 @@
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1406491
-</t>
+          <t>2124</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="X11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11812 1
-</t>
-        </is>
-      </c>
-      <c r="Y11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02 4
-</t>
-        </is>
-      </c>
-      <c r="Z11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="n"/>
+      <c r="W11" s="2" t="n"/>
+      <c r="X11" s="2" t="n"/>
+      <c r="Y11" s="2" t="n"/>
+      <c r="Z11" s="2" t="n"/>
       <c r="AA11" t="inlineStr">
         <is>
           <t>6</t>
@@ -1835,109 +1638,92 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2295
-</t>
+          <t>2295</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1839
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9318
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>745</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr"/>
@@ -1949,8 +1735,7 @@
       <c r="W12" s="2" t="inlineStr"/>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
@@ -1960,8 +1745,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1978,146 +1762,122 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3220
-</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
-</t>
+          <t>945</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>745</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2134,146 +1894,122 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3240
-</t>
+          <t>324</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">001
-</t>
+          <t>949</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>905</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">719
-</t>
+          <t>719</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2290,146 +2026,122 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3079
-</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0911
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
-</t>
+          <t>730</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2446,14 +2158,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1475
-</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2463,20 +2173,17 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
-</t>
+          <t>474</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1644
-</t>
+          <t>644</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2486,20 +2193,17 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
-</t>
+          <t>465</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">732
-</t>
+          <t>732</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2509,20 +2213,17 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11404
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2532,8 +2233,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
+          <t>835</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2543,44 +2243,37 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3945
-</t>
+          <t>3945</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">843
-</t>
+          <t>843</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">786
-</t>
+          <t>786</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">851
-</t>
+          <t>861</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12088
-</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2597,140 +2290,117 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2950
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">088
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28 14
-</t>
+          <t>12 14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2695
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
-</t>
+          <t>929</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>789</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>901</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -2752,26 +2422,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4283
-</t>
+          <t>4285</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2781,20 +2447,17 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2804,26 +2467,22 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr"/>
@@ -2834,14 +2493,12 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
@@ -2851,8 +2508,7 @@
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2862,14 +2518,12 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1701
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
@@ -2879,8 +2533,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2897,146 +2550,122 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4406
-</t>
+          <t>406</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2149
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">540
-</t>
+          <t>540</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1870
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>810</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3053,38 +2682,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531
-</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -3094,20 +2717,17 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -3117,80 +2737,67 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">768
-</t>
+          <t>768</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3207,146 +2814,122 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2617
-</t>
+          <t>2517</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
-</t>
+          <t>908</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
-</t>
+          <t>740</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3363,134 +2946,112 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233
-</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
-</t>
+          <t>740</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
@@ -3500,8 +3061,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3523,39 +3083,33 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1131
-</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>694</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
-</t>
+          <t>925</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
-</t>
+          <t>437</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
-</t>
+          <t>612</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3565,14 +3119,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>762</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>722</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3582,50 +3134,42 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1090
-</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
-</t>
+          <t>905</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3479
-</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">406
-</t>
+          <t>406</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
-</t>
+          <t>913</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3640,14 +3184,12 @@
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9295
-</t>
+          <t>355</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3664,146 +3206,122 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2154
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10434
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2211
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">696
-</t>
+          <t>696</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">871
-</t>
+          <t>871</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3820,26 +3338,22 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3864,51 +3378,43 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1842
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">915
-</t>
+          <t>915</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr"/>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
@@ -3923,14 +3429,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
@@ -3940,14 +3444,12 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
-</t>
+          <t>940</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3964,146 +3466,122 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1846
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2088
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
-</t>
+          <t>730</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
-</t>
+          <t>885</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4120,141 +3598,118 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>2888</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
-</t>
+          <t>940</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2108
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7170
-</t>
+          <t>770</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4271,98 +3726,82 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
-</t>
+          <t>3059</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
@@ -4372,44 +3811,37 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">728
-</t>
+          <t>728</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">838
-</t>
+          <t>830</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2898
-</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4426,146 +3858,122 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2898
-</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>700</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1821
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4582,21 +3990,18 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16099
-</t>
+          <t>16099</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11298
-</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
-</t>
+          <t>906</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -4606,39 +4011,33 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">866
-</t>
+          <t>666</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">386
-</t>
+          <t>356</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>717</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>798</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -4653,62 +4052,52 @@
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1052
-</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
-</t>
+          <t>874</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
-</t>
+          <t>901</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5610
-</t>
+          <t>3619</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">345
-</t>
+          <t>346</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
-</t>
+          <t>811</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
-</t>
+          <t>885</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4410
-</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4725,136 +4114,114 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3220
-</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>798</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>941</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2144
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4871,33 +4238,28 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>2355</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -4907,20 +4269,17 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -4930,80 +4289,67 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
+          <t>830</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -5020,146 +4366,122 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14828
-</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1826
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">865
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1848
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>515</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
-</t>
+          <t>770</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5176,14 +4498,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4828
-</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1441
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -5193,122 +4513,102 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11095
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
-</t>
+          <t>568</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>810</t>
         </is>
       </c>
       <c r="Z34" s="2" t="n"/>
@@ -5326,32 +4626,27 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94928
-</t>
+          <t>4928</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -5366,104 +4661,87 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2945
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6008
-</t>
+          <t>600</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
-</t>
+          <t>755</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5480,146 +4758,122 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94989
-</t>
+          <t>989</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2942
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1866
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1881
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
-</t>
+          <t>551</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1666
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
-</t>
+          <t>798</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5636,14 +4890,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21928
-</t>
+          <t>1928</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -5658,110 +4910,89 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">533
-</t>
+          <t>533</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">757
-</t>
+          <t>757</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7112
-</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">716
-</t>
-        </is>
-      </c>
+          <t>027</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="n"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>44203</t>
+          <t>4490</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
-</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>848</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2348
-</t>
+          <t>548</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">804
-</t>
+          <t>804</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>855</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4098
-</t>
+          <t>095</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -5783,50 +5014,42 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">438
-</t>
+          <t>4386</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K38" s="2" t="n"/>
@@ -5837,86 +5060,72 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">827
-</t>
+          <t>627</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
-</t>
+          <t>819</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
-</t>
+          <t>898</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5933,69 +5142,54 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">395953
-</t>
+          <t>5953</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8115
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">016
-</t>
+          <t>016</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -6005,32 +5199,27 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1209
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
-</t>
+          <t>520</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -6041,14 +5230,12 @@
       <c r="V39" s="2" t="inlineStr"/>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
@@ -6080,32 +5267,27 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -6120,98 +5302,82 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">008
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">588
-</t>
+          <t>585</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>820</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6228,146 +5394,122 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4084
-</t>
+          <t>4084</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
-</t>
+          <t>889</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">622
-</t>
+          <t>625</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
-</t>
+          <t>820</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6384,146 +5526,122 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3401
-</t>
+          <t>3401</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">605
-</t>
+          <t>605</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3310
-</t>
+          <t>5370</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6540,146 +5658,122 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5571
-</t>
+          <t>5571</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1996
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
+          <t>580</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1354
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6696,141 +5790,118 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1836
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr"/>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1867
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">593
-</t>
+          <t>595</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6847,146 +5918,122 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29830
-</t>
+          <t>29830</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1417
-</t>
+          <t>1417</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1911
-</t>
+          <t>971</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
-</t>
+          <t>620</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>708</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
-</t>
+          <t>894</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>830</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>919</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">53409
-</t>
+          <t>5409</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1024
-</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
-</t>
+          <t>975</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3510
-</t>
+          <t>3510</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">690
-</t>
+          <t>690</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11115
-</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">955
-</t>
+          <t>959</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
-</t>
+          <t>996</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4668
-</t>
+          <t>4688</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -7003,146 +6050,122 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4970
-</t>
+          <t>4970</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">006
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
-</t>
+          <t>901</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">585
-</t>
+          <t>585</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>554</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">

--- a/results/05_transient_transcription_output/601/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/601/Midpoint_Excel_with_OCR_Results.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>5853</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>270</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -716,12 +716,12 @@
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>152</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>2107</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr"/>
@@ -747,7 +747,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>239</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>279</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>152</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>290</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>173</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>282</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>282</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>220</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1138,69 +1138,69 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2296</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>403</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
           <t>08</t>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>190</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>22249</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1320,12 +1320,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>601</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>1664</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>3126</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9 21</t>
+          <t>22 95</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>625</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>102</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>153</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>192</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2124</t>
+          <t>226</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>170</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>920</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       <c r="W12" s="2" t="inlineStr"/>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>175</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>3240</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>715</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>960</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>72</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
@@ -2158,12 +2158,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1475</t>
+          <t>14752</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>463</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2213,12 +2213,12 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>145</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>832</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>242</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>4502</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -2290,22 +2290,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>2950</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>280</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>189</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12 14</t>
+          <t>0 14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>102</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2345,12 +2345,12 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>021</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>154</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>180</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>406</t>
+          <t>4406</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>190</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>200</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>199</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>148</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>22</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2517</t>
+          <t>2617</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>162</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>220</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>161</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>912</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>613</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>903</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>228</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>4355</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>2954</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>129</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>160</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>929</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>157</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>158</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>173</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2888</t>
+          <t>2878</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>170</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>138</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>338</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>212</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>217</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>792</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3619</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>878</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4161,12 +4161,12 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>08</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>160</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>181 1</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>723</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>112</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>172</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>222</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>4828</t>
+          <t>14828</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>266</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>140</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>193</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>167</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>176</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>900</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>4989</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4813,7 +4813,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>172</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>790</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>1928</t>
+          <t>21928</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>3134</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>853</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>095</t>
+          <t>4092</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>132</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>106</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>123</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>08</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>152</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5170,7 +5170,11 @@
           <t>120</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr">
         <is>
@@ -5179,12 +5183,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>288</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>115</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -5267,7 +5271,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>245</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -5282,7 +5286,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -5317,7 +5321,7 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>101</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -5367,7 +5371,7 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>162</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
@@ -5404,7 +5408,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5484,7 +5488,7 @@
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>106</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
@@ -5494,7 +5498,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>170</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
@@ -5536,7 +5540,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>141</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5576,7 +5580,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>226</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5631,12 +5635,12 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>182</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>870</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5713,7 +5717,7 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>162</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -5753,12 +5757,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>172</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>152</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
@@ -5773,7 +5777,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5790,7 +5794,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5866,7 +5870,7 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>169</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
@@ -5896,12 +5900,12 @@
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>720</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5928,7 +5932,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5973,7 +5977,7 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>918</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -5988,7 +5992,7 @@
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>137</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
@@ -6018,7 +6022,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>222</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
@@ -6028,7 +6032,7 @@
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>4688</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -6070,7 +6074,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>103</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -6090,7 +6094,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -6100,7 +6104,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>080</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -6155,12 +6159,12 @@
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>114</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>190</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">

--- a/results/05_transient_transcription_output/601/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/601/Midpoint_Excel_with_OCR_Results.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>5853</t>
+          <t>585</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>207</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr"/>
@@ -742,7 +742,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>388</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>155</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -797,12 +797,12 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>185</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>267</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>15</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>155</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>28</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>17</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>188</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>870</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1061,12 +1061,12 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>224</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>188</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>280</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22249</t>
+          <t>2229</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1320,12 +1320,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>681</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1664</t>
+          <t>164</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22 95</t>
+          <t>2 25</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>103</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>152</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>20</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>130</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>940</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>14752</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>912</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>124</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>835</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>248</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>4502</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>230</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>136</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>202</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2345,12 +2345,12 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>021</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>155</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>80</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>170</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>207</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>09</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>178</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>54</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>168</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>155</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>165</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>913</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3103,13 +3103,13 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>643</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>93</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>913</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>922</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>400</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>118</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -3741,69 +3741,69 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>838</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>950</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
           <t>415</t>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>838</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3612</t>
+          <t>361</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>05</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>181 1</t>
+          <t>181 2</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>22</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>14828</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>286</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>13</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>133</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>17</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>185</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>4092</t>
+          <t>4090</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -5170,11 +5170,7 @@
           <t>120</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr">
         <is>
@@ -5183,17 +5179,17 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>160</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>016</t>
+          <t>301</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -5286,7 +5282,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -5321,7 +5317,7 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -5371,12 +5367,12 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>163</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>720</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5408,7 +5404,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5453,7 +5449,7 @@
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>198</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -5498,7 +5494,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>178</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
@@ -5580,7 +5576,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>133</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5640,7 +5636,7 @@
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>880</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5777,7 +5773,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5794,7 +5790,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5870,7 +5866,7 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>159</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
@@ -5922,7 +5918,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>29830</t>
+          <t>2980</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -6022,7 +6018,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>955</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
@@ -6094,7 +6090,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -6104,7 +6100,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>080</t>
+          <t>084</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -6159,7 +6155,7 @@
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
@@ -6169,7 +6165,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
